--- a/research/traditional_assets/database/data/lithuania/lithuania_hotel_gaming.xlsx
+++ b/research/traditional_assets/database/data/lithuania/lithuania_hotel_gaming.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="nsel_ntu1l" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,22 +590,22 @@
         </is>
       </c>
       <c r="G2">
-        <v>-0.04759238521836506</v>
+        <v>0.01517278617710583</v>
       </c>
       <c r="H2">
-        <v>-0.04759238521836506</v>
+        <v>0.01517278617710583</v>
       </c>
       <c r="I2">
-        <v>0.0007502799552071669</v>
+        <v>0.01058315334773218</v>
       </c>
       <c r="J2">
-        <v>0.0007502799552071669</v>
+        <v>0.008098412996525495</v>
       </c>
       <c r="K2">
-        <v>-1.11</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L2">
-        <v>-0.01243001119820829</v>
+        <v>0.0004697624190064795</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +614,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,76 +623,70 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>21.6</v>
+        <v>12.5</v>
       </c>
       <c r="V2">
-        <v>0.6390532544378699</v>
+        <v>0.5165289256198348</v>
       </c>
       <c r="W2">
-        <v>-0.06132596685082873</v>
+        <v>0.004915254237288135</v>
       </c>
       <c r="X2">
-        <v>0.07429610936909035</v>
+        <v>0.1198628132176125</v>
       </c>
       <c r="Y2">
-        <v>-0.1356220762199191</v>
-      </c>
-      <c r="Z2">
-        <v>-21.11111111111112</v>
-      </c>
-      <c r="AA2">
-        <v>-0.01583924349881798</v>
+        <v>-0.1149475589803244</v>
       </c>
       <c r="AB2">
-        <v>0.06309951075624839</v>
-      </c>
-      <c r="AC2">
-        <v>-0.07893875425506637</v>
+        <v>0.09473226671692191</v>
       </c>
       <c r="AD2">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>11.4</v>
+        <v>13.3</v>
       </c>
       <c r="AG2">
-        <v>-10.2</v>
+        <v>0.8000000000000007</v>
       </c>
       <c r="AH2">
-        <v>0.252212389380531</v>
+        <v>0.3546666666666667</v>
       </c>
       <c r="AI2">
-        <v>0.3917525773195876</v>
+        <v>0.4683098591549296</v>
       </c>
       <c r="AJ2">
-        <v>-0.4322033898305086</v>
+        <v>0.03200000000000003</v>
       </c>
       <c r="AK2">
-        <v>-1.360000000000001</v>
+        <v>0.05031446540880508</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AM2">
-        <v>-0.887</v>
+        <v>1.35</v>
       </c>
       <c r="AN2">
-        <v>114</v>
+        <v>6.855670103092784</v>
+      </c>
+      <c r="AO2">
+        <v>1.281045751633987</v>
       </c>
       <c r="AP2">
-        <v>-102</v>
+        <v>0.4123711340206189</v>
       </c>
       <c r="AQ2">
-        <v>-0.07553551296505073</v>
+        <v>1.451851851851852</v>
       </c>
     </row>
     <row r="3">
@@ -710,22 +706,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>-0.04759238521836506</v>
+        <v>0.01517278617710583</v>
       </c>
       <c r="H3">
-        <v>-0.04759238521836506</v>
+        <v>0.01517278617710583</v>
       </c>
       <c r="I3">
-        <v>0.0007502799552071669</v>
+        <v>0.01058315334773218</v>
       </c>
       <c r="J3">
-        <v>0.0007502799552071669</v>
+        <v>0.008098412996525495</v>
       </c>
       <c r="K3">
-        <v>-1.11</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="L3">
-        <v>-0.01243001119820829</v>
+        <v>0.0004697624190064795</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -734,7 +730,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -743,76 +739,8782 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>21.6</v>
+        <v>12.5</v>
       </c>
       <c r="V3">
-        <v>0.6390532544378699</v>
+        <v>0.5165289256198348</v>
       </c>
       <c r="W3">
-        <v>-0.06132596685082873</v>
+        <v>0.004915254237288135</v>
       </c>
       <c r="X3">
-        <v>0.07429610936909035</v>
+        <v>0.1198628132176125</v>
       </c>
       <c r="Y3">
-        <v>-0.1356220762199191</v>
+        <v>-0.1149475589803244</v>
+      </c>
+      <c r="AB3">
+        <v>0.09473226671692191</v>
+      </c>
+      <c r="AD3">
+        <v>13.3</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>13.3</v>
+      </c>
+      <c r="AG3">
+        <v>0.8000000000000007</v>
+      </c>
+      <c r="AH3">
+        <v>0.3546666666666667</v>
+      </c>
+      <c r="AI3">
+        <v>0.4683098591549296</v>
+      </c>
+      <c r="AJ3">
+        <v>0.03200000000000003</v>
+      </c>
+      <c r="AK3">
+        <v>0.05031446540880508</v>
+      </c>
+      <c r="AL3">
+        <v>1.53</v>
+      </c>
+      <c r="AM3">
+        <v>1.35</v>
+      </c>
+      <c r="AN3">
+        <v>6.855670103092784</v>
+      </c>
+      <c r="AO3">
+        <v>1.281045751633987</v>
+      </c>
+      <c r="AP3">
+        <v>0.4123711340206189</v>
+      </c>
+      <c r="AQ3">
+        <v>1.451851851851852</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Novaturas AB (NSEL:NTU1L)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>NSEL:NTU1L</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Hotel/Gaming</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.354666666666667</v>
+      </c>
+      <c r="F2">
+        <v>0.1</v>
+      </c>
+      <c r="G2">
+        <v>24.2</v>
+      </c>
+      <c r="H2">
+        <v>34.3770690105566</v>
+      </c>
+      <c r="I2">
+        <v>25</v>
+      </c>
+      <c r="J2">
+        <v>25.6270690105566</v>
+      </c>
+      <c r="K2">
+        <v>13.3</v>
+      </c>
+      <c r="L2">
+        <v>3.75</v>
+      </c>
+      <c r="M2">
+        <v>0.09473226671692191</v>
+      </c>
+      <c r="N2">
+        <v>0.09336365951748291</v>
+      </c>
+      <c r="O2">
+        <v>0.0490060091743119</v>
+      </c>
+      <c r="P2">
+        <v>0.040205</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Caa/CCC</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.119862813217613</v>
+      </c>
+      <c r="T2">
+        <v>0.0992701772416477</v>
+      </c>
+      <c r="U2">
+        <v>1.0991837452458</v>
+      </c>
+      <c r="V2">
+        <v>0.819954714842172</v>
+      </c>
+      <c r="W2">
+        <v>11.05003523608175</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>24.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.07374819139040771</v>
+      </c>
+      <c r="AC2">
+        <v>0.05765412844036698</v>
+      </c>
+      <c r="AD2">
+        <v>0.15</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>1</v>
+      </c>
+      <c r="AG2">
+        <v>1.94</v>
+      </c>
+      <c r="AH2">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="AI2">
+        <v>0.3140000000000001</v>
+      </c>
+      <c r="AJ2">
+        <v>13.3</v>
+      </c>
+      <c r="AK2">
+        <v>13.3</v>
+      </c>
+      <c r="AL2">
+        <v>1.53</v>
+      </c>
+      <c r="AM2">
+        <v>13.3</v>
+      </c>
+      <c r="AN2">
+        <v>12.5</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AQ2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.09405193859642932</v>
+      </c>
+      <c r="C2">
+        <v>37.80782997745193</v>
+      </c>
+      <c r="D2">
+        <v>25.30782997745193</v>
+      </c>
+      <c r="E2">
+        <v>-13.3</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>12.5</v>
+      </c>
+      <c r="H2">
+        <v>24.2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>1.94</v>
+      </c>
+      <c r="K2">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L2">
+        <v>1.96</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.96</v>
+      </c>
+      <c r="O2">
+        <v>0.294</v>
+      </c>
+      <c r="P2">
+        <v>1.666</v>
+      </c>
+      <c r="Q2">
+        <v>1.646</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.09405193859642932</v>
+      </c>
+      <c r="T2">
+        <v>0.749197201378634</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0.15</v>
+      </c>
+      <c r="W2">
+        <v>0.038845</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.09396951068853468</v>
+      </c>
+      <c r="C3">
+        <v>37.47064201262063</v>
+      </c>
+      <c r="D3">
+        <v>25.34564201262063</v>
+      </c>
+      <c r="E3">
+        <v>-12.925</v>
+      </c>
+      <c r="F3">
+        <v>0.375</v>
+      </c>
+      <c r="G3">
+        <v>12.5</v>
+      </c>
+      <c r="H3">
+        <v>24.2</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>1.94</v>
+      </c>
+      <c r="K3">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L3">
+        <v>1.96</v>
+      </c>
+      <c r="M3">
+        <v>0.0171375</v>
+      </c>
+      <c r="N3">
+        <v>1.9428625</v>
+      </c>
+      <c r="O3">
+        <v>0.291429375</v>
+      </c>
+      <c r="P3">
+        <v>1.651433125</v>
+      </c>
+      <c r="Q3">
+        <v>1.631433125</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.09452632392781281</v>
+      </c>
+      <c r="T3">
+        <v>0.7556297026025919</v>
+      </c>
+      <c r="U3">
+        <v>0.0457</v>
+      </c>
+      <c r="V3">
+        <v>0.15</v>
+      </c>
+      <c r="W3">
+        <v>0.038845</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>114.3690736688549</v>
       </c>
       <c r="Z3">
-        <v>-21.11111111111112</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01583924349881798</v>
-      </c>
-      <c r="AB3">
-        <v>0.06309951075624839</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07893875425506637</v>
-      </c>
-      <c r="AD3">
-        <v>11.4</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>11.4</v>
-      </c>
-      <c r="AG3">
-        <v>-10.2</v>
-      </c>
-      <c r="AH3">
-        <v>0.252212389380531</v>
-      </c>
-      <c r="AI3">
-        <v>0.3917525773195876</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.4322033898305086</v>
-      </c>
-      <c r="AK3">
-        <v>-1.360000000000001</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-0.887</v>
-      </c>
-      <c r="AN3">
-        <v>114</v>
-      </c>
-      <c r="AP3">
-        <v>-102</v>
-      </c>
-      <c r="AQ3">
-        <v>-0.07553551296505073</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.09388708278064005</v>
+      </c>
+      <c r="C4">
+        <v>37.133567205604</v>
+      </c>
+      <c r="D4">
+        <v>25.383567205604</v>
+      </c>
+      <c r="E4">
+        <v>-12.55</v>
+      </c>
+      <c r="F4">
+        <v>0.75</v>
+      </c>
+      <c r="G4">
+        <v>12.5</v>
+      </c>
+      <c r="H4">
+        <v>24.2</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1.94</v>
+      </c>
+      <c r="K4">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L4">
+        <v>1.96</v>
+      </c>
+      <c r="M4">
+        <v>0.034275</v>
+      </c>
+      <c r="N4">
+        <v>1.925725</v>
+      </c>
+      <c r="O4">
+        <v>0.2888587500000001</v>
+      </c>
+      <c r="P4">
+        <v>1.63686625</v>
+      </c>
+      <c r="Q4">
+        <v>1.61686625</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.09501039059248985</v>
+      </c>
+      <c r="T4">
+        <v>0.7621934793617329</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0.15</v>
+      </c>
+      <c r="W4">
+        <v>0.038845</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>57.18453683442742</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.09380465487274538</v>
+      </c>
+      <c r="C5">
+        <v>36.79660606512421</v>
+      </c>
+      <c r="D5">
+        <v>25.42160606512421</v>
+      </c>
+      <c r="E5">
+        <v>-12.175</v>
+      </c>
+      <c r="F5">
+        <v>1.125</v>
+      </c>
+      <c r="G5">
+        <v>12.5</v>
+      </c>
+      <c r="H5">
+        <v>24.2</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>1.94</v>
+      </c>
+      <c r="K5">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L5">
+        <v>1.96</v>
+      </c>
+      <c r="M5">
+        <v>0.05141250000000001</v>
+      </c>
+      <c r="N5">
+        <v>1.9085875</v>
+      </c>
+      <c r="O5">
+        <v>0.286288125</v>
+      </c>
+      <c r="P5">
+        <v>1.622299375</v>
+      </c>
+      <c r="Q5">
+        <v>1.602299375</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.09550443801313957</v>
+      </c>
+      <c r="T5">
+        <v>0.7688925917241547</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0.15</v>
+      </c>
+      <c r="W5">
+        <v>0.038845</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>38.12302455628495</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.09372222696485075</v>
+      </c>
+      <c r="C6">
+        <v>36.45975910295734</v>
+      </c>
+      <c r="D6">
+        <v>25.45975910295734</v>
+      </c>
+      <c r="E6">
+        <v>-11.8</v>
+      </c>
+      <c r="F6">
+        <v>1.5</v>
+      </c>
+      <c r="G6">
+        <v>12.5</v>
+      </c>
+      <c r="H6">
+        <v>24.2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1.94</v>
+      </c>
+      <c r="K6">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L6">
+        <v>1.96</v>
+      </c>
+      <c r="M6">
+        <v>0.06855</v>
+      </c>
+      <c r="N6">
+        <v>1.89145</v>
+      </c>
+      <c r="O6">
+        <v>0.2837175</v>
+      </c>
+      <c r="P6">
+        <v>1.6077325</v>
+      </c>
+      <c r="Q6">
+        <v>1.5877325</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.0960087780883862</v>
+      </c>
+      <c r="T6">
+        <v>0.7757312689274606</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0.15</v>
+      </c>
+      <c r="W6">
+        <v>0.038845</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>28.59226841721371</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.09363979905695612</v>
+      </c>
+      <c r="C7">
+        <v>36.12302683395647</v>
+      </c>
+      <c r="D7">
+        <v>25.49802683395647</v>
+      </c>
+      <c r="E7">
+        <v>-11.425</v>
+      </c>
+      <c r="F7">
+        <v>1.875</v>
+      </c>
+      <c r="G7">
+        <v>12.5</v>
+      </c>
+      <c r="H7">
+        <v>24.2</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1.94</v>
+      </c>
+      <c r="K7">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L7">
+        <v>1.96</v>
+      </c>
+      <c r="M7">
+        <v>0.08568750000000001</v>
+      </c>
+      <c r="N7">
+        <v>1.8743125</v>
+      </c>
+      <c r="O7">
+        <v>0.2811468750000001</v>
+      </c>
+      <c r="P7">
+        <v>1.593165625</v>
+      </c>
+      <c r="Q7">
+        <v>1.573165625</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.09652373584942749</v>
+      </c>
+      <c r="T7">
+        <v>0.782713918282415</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0.15</v>
+      </c>
+      <c r="W7">
+        <v>0.038845</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>22.87381473377097</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.09355737114906147</v>
+      </c>
+      <c r="C8">
+        <v>35.78640977607476</v>
+      </c>
+      <c r="D8">
+        <v>25.53640977607476</v>
+      </c>
+      <c r="E8">
+        <v>-11.05</v>
+      </c>
+      <c r="F8">
+        <v>2.25</v>
+      </c>
+      <c r="G8">
+        <v>12.5</v>
+      </c>
+      <c r="H8">
+        <v>24.2</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1.94</v>
+      </c>
+      <c r="K8">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L8">
+        <v>1.96</v>
+      </c>
+      <c r="M8">
+        <v>0.102825</v>
+      </c>
+      <c r="N8">
+        <v>1.857175</v>
+      </c>
+      <c r="O8">
+        <v>0.27857625</v>
+      </c>
+      <c r="P8">
+        <v>1.57859875</v>
+      </c>
+      <c r="Q8">
+        <v>1.55859875</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.09704965015857603</v>
+      </c>
+      <c r="T8">
+        <v>0.7898451346449216</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0.15</v>
+      </c>
+      <c r="W8">
+        <v>0.038845</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>19.06151227814247</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.09347494324116681</v>
+      </c>
+      <c r="C9">
+        <v>35.44990845038885</v>
+      </c>
+      <c r="D9">
+        <v>25.57490845038884</v>
+      </c>
+      <c r="E9">
+        <v>-10.675</v>
+      </c>
+      <c r="F9">
+        <v>2.625</v>
+      </c>
+      <c r="G9">
+        <v>12.5</v>
+      </c>
+      <c r="H9">
+        <v>24.2</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1.94</v>
+      </c>
+      <c r="K9">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L9">
+        <v>1.96</v>
+      </c>
+      <c r="M9">
+        <v>0.1199625</v>
+      </c>
+      <c r="N9">
+        <v>1.8400375</v>
+      </c>
+      <c r="O9">
+        <v>0.276005625</v>
+      </c>
+      <c r="P9">
+        <v>1.564031875</v>
+      </c>
+      <c r="Q9">
+        <v>1.544031875</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.09758687445286754</v>
+      </c>
+      <c r="T9">
+        <v>0.797129710499095</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0.15</v>
+      </c>
+      <c r="W9">
+        <v>0.038845</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>16.33843909555069</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.09339251533327218</v>
+      </c>
+      <c r="C10">
+        <v>35.11352338112236</v>
+      </c>
+      <c r="D10">
+        <v>25.61352338112236</v>
+      </c>
+      <c r="E10">
+        <v>-10.3</v>
+      </c>
+      <c r="F10">
+        <v>3</v>
+      </c>
+      <c r="G10">
+        <v>12.5</v>
+      </c>
+      <c r="H10">
+        <v>24.2</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>1.94</v>
+      </c>
+      <c r="K10">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L10">
+        <v>1.96</v>
+      </c>
+      <c r="M10">
+        <v>0.1371</v>
+      </c>
+      <c r="N10">
+        <v>1.8229</v>
+      </c>
+      <c r="O10">
+        <v>0.273435</v>
+      </c>
+      <c r="P10">
+        <v>1.549465</v>
+      </c>
+      <c r="Q10">
+        <v>1.529465</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.09813577753616541</v>
+      </c>
+      <c r="T10">
+        <v>0.8045726466979244</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0.15</v>
+      </c>
+      <c r="W10">
+        <v>0.038845</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>14.29613420860686</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.09343248742537753</v>
+      </c>
+      <c r="C11">
+        <v>34.71978313765218</v>
+      </c>
+      <c r="D11">
+        <v>25.59478313765218</v>
+      </c>
+      <c r="E11">
+        <v>-9.925000000000001</v>
+      </c>
+      <c r="F11">
+        <v>3.375</v>
+      </c>
+      <c r="G11">
+        <v>12.5</v>
+      </c>
+      <c r="H11">
+        <v>24.2</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>1.94</v>
+      </c>
+      <c r="K11">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L11">
+        <v>1.96</v>
+      </c>
+      <c r="M11">
+        <v>0.1596375</v>
+      </c>
+      <c r="N11">
+        <v>1.8003625</v>
+      </c>
+      <c r="O11">
+        <v>0.270054375</v>
+      </c>
+      <c r="P11">
+        <v>1.530308125</v>
+      </c>
+      <c r="Q11">
+        <v>1.510308125</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.0986967444234918</v>
+      </c>
+      <c r="T11">
+        <v>0.8121791639121125</v>
+      </c>
+      <c r="U11">
+        <v>0.0473</v>
+      </c>
+      <c r="V11">
+        <v>0.15</v>
+      </c>
+      <c r="W11">
+        <v>0.040205</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>12.27781692897972</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.09336365951748289</v>
+      </c>
+      <c r="C12">
+        <v>34.3770690105566</v>
+      </c>
+      <c r="D12">
+        <v>25.6270690105566</v>
+      </c>
+      <c r="E12">
+        <v>-9.550000000000001</v>
+      </c>
+      <c r="F12">
+        <v>3.75</v>
+      </c>
+      <c r="G12">
+        <v>12.5</v>
+      </c>
+      <c r="H12">
+        <v>24.2</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>1.94</v>
+      </c>
+      <c r="K12">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L12">
+        <v>1.96</v>
+      </c>
+      <c r="M12">
+        <v>0.177375</v>
+      </c>
+      <c r="N12">
+        <v>1.782625</v>
+      </c>
+      <c r="O12">
+        <v>0.26739375</v>
+      </c>
+      <c r="P12">
+        <v>1.51523125</v>
+      </c>
+      <c r="Q12">
+        <v>1.49523125</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.09927017724164766</v>
+      </c>
+      <c r="T12">
+        <v>0.8199547148421718</v>
+      </c>
+      <c r="U12">
+        <v>0.0473</v>
+      </c>
+      <c r="V12">
+        <v>0.15</v>
+      </c>
+      <c r="W12">
+        <v>0.040205</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>11.05003523608175</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.09365013160958825</v>
+      </c>
+      <c r="C13">
+        <v>33.86822356919582</v>
+      </c>
+      <c r="D13">
+        <v>25.49322356919582</v>
+      </c>
+      <c r="E13">
+        <v>-9.175000000000001</v>
+      </c>
+      <c r="F13">
+        <v>4.125</v>
+      </c>
+      <c r="G13">
+        <v>12.5</v>
+      </c>
+      <c r="H13">
+        <v>24.2</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>1.94</v>
+      </c>
+      <c r="K13">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L13">
+        <v>1.96</v>
+      </c>
+      <c r="M13">
+        <v>0.2107875</v>
+      </c>
+      <c r="N13">
+        <v>1.7492125</v>
+      </c>
+      <c r="O13">
+        <v>0.262381875</v>
+      </c>
+      <c r="P13">
+        <v>1.486830625</v>
+      </c>
+      <c r="Q13">
+        <v>1.466830625</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.09985649619054859</v>
+      </c>
+      <c r="T13">
+        <v>0.8279049972538051</v>
+      </c>
+      <c r="U13">
+        <v>0.0511</v>
+      </c>
+      <c r="V13">
+        <v>0.15</v>
+      </c>
+      <c r="W13">
+        <v>0.043435</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>9.298464092984641</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.0936136037016936</v>
+      </c>
+      <c r="C14">
+        <v>33.51021231030361</v>
+      </c>
+      <c r="D14">
+        <v>25.51021231030361</v>
+      </c>
+      <c r="E14">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="F14">
+        <v>4.5</v>
+      </c>
+      <c r="G14">
+        <v>12.5</v>
+      </c>
+      <c r="H14">
+        <v>24.2</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>1.94</v>
+      </c>
+      <c r="K14">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L14">
+        <v>1.96</v>
+      </c>
+      <c r="M14">
+        <v>0.22995</v>
+      </c>
+      <c r="N14">
+        <v>1.73005</v>
+      </c>
+      <c r="O14">
+        <v>0.2595075</v>
+      </c>
+      <c r="P14">
+        <v>1.4705425</v>
+      </c>
+      <c r="Q14">
+        <v>1.4505425</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1004561405701064</v>
+      </c>
+      <c r="T14">
+        <v>0.8360359679020666</v>
+      </c>
+      <c r="U14">
+        <v>0.0511</v>
+      </c>
+      <c r="V14">
+        <v>0.15</v>
+      </c>
+      <c r="W14">
+        <v>0.043435</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>8.52359208523592</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.09357707579379895</v>
+      </c>
+      <c r="C15">
+        <v>33.1522237091806</v>
+      </c>
+      <c r="D15">
+        <v>25.52722370918061</v>
+      </c>
+      <c r="E15">
+        <v>-8.425000000000001</v>
+      </c>
+      <c r="F15">
+        <v>4.875</v>
+      </c>
+      <c r="G15">
+        <v>12.5</v>
+      </c>
+      <c r="H15">
+        <v>24.2</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>1.94</v>
+      </c>
+      <c r="K15">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L15">
+        <v>1.96</v>
+      </c>
+      <c r="M15">
+        <v>0.2491125</v>
+      </c>
+      <c r="N15">
+        <v>1.7108875</v>
+      </c>
+      <c r="O15">
+        <v>0.256633125</v>
+      </c>
+      <c r="P15">
+        <v>1.454254375</v>
+      </c>
+      <c r="Q15">
+        <v>1.434254375</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1010695698779298</v>
+      </c>
+      <c r="T15">
+        <v>0.8443538574158053</v>
+      </c>
+      <c r="U15">
+        <v>0.0511</v>
+      </c>
+      <c r="V15">
+        <v>0.15</v>
+      </c>
+      <c r="W15">
+        <v>0.043435</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>7.867931155602388</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.09376664788590432</v>
+      </c>
+      <c r="C16">
+        <v>32.68918397253456</v>
+      </c>
+      <c r="D16">
+        <v>25.43918397253456</v>
+      </c>
+      <c r="E16">
+        <v>-8.050000000000001</v>
+      </c>
+      <c r="F16">
+        <v>5.250000000000001</v>
+      </c>
+      <c r="G16">
+        <v>12.5</v>
+      </c>
+      <c r="H16">
+        <v>24.2</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>1.94</v>
+      </c>
+      <c r="K16">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L16">
+        <v>1.96</v>
+      </c>
+      <c r="M16">
+        <v>0.2782500000000001</v>
+      </c>
+      <c r="N16">
+        <v>1.68175</v>
+      </c>
+      <c r="O16">
+        <v>0.2522625</v>
+      </c>
+      <c r="P16">
+        <v>1.4294875</v>
+      </c>
+      <c r="Q16">
+        <v>1.4094875</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1016972649836097</v>
+      </c>
+      <c r="T16">
+        <v>0.8528651862205612</v>
+      </c>
+      <c r="U16">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V16">
+        <v>0.15</v>
+      </c>
+      <c r="W16">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>7.044025157232703</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.09374626997800967</v>
+      </c>
+      <c r="C17">
+        <v>32.32361859563299</v>
+      </c>
+      <c r="D17">
+        <v>25.44861859563299</v>
+      </c>
+      <c r="E17">
+        <v>-7.675000000000001</v>
+      </c>
+      <c r="F17">
+        <v>5.625</v>
+      </c>
+      <c r="G17">
+        <v>12.5</v>
+      </c>
+      <c r="H17">
+        <v>24.2</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>1.94</v>
+      </c>
+      <c r="K17">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L17">
+        <v>1.96</v>
+      </c>
+      <c r="M17">
+        <v>0.298125</v>
+      </c>
+      <c r="N17">
+        <v>1.661875</v>
+      </c>
+      <c r="O17">
+        <v>0.24928125</v>
+      </c>
+      <c r="P17">
+        <v>1.41259375</v>
+      </c>
+      <c r="Q17">
+        <v>1.39259375</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1023397293858937</v>
+      </c>
+      <c r="T17">
+        <v>0.8615767815854291</v>
+      </c>
+      <c r="U17">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V17">
+        <v>0.15</v>
+      </c>
+      <c r="W17">
+        <v>0.04505000000000001</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>6.574423480083857</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09399789207011502</v>
+      </c>
+      <c r="C18">
+        <v>31.83260991464766</v>
+      </c>
+      <c r="D18">
+        <v>25.33260991464766</v>
+      </c>
+      <c r="E18">
+        <v>-7.300000000000001</v>
+      </c>
+      <c r="F18">
+        <v>6</v>
+      </c>
+      <c r="G18">
+        <v>12.5</v>
+      </c>
+      <c r="H18">
+        <v>24.2</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>1.94</v>
+      </c>
+      <c r="K18">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L18">
+        <v>1.96</v>
+      </c>
+      <c r="M18">
+        <v>0.33</v>
+      </c>
+      <c r="N18">
+        <v>1.63</v>
+      </c>
+      <c r="O18">
+        <v>0.2445</v>
+      </c>
+      <c r="P18">
+        <v>1.3855</v>
+      </c>
+      <c r="Q18">
+        <v>1.3655</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1029974905596607</v>
+      </c>
+      <c r="T18">
+        <v>0.8704957958875558</v>
+      </c>
+      <c r="U18">
+        <v>0.055</v>
+      </c>
+      <c r="V18">
+        <v>0.15</v>
+      </c>
+      <c r="W18">
+        <v>0.04675</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>5.939393939393939</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09399451416222038</v>
+      </c>
+      <c r="C19">
+        <v>31.45916027203955</v>
+      </c>
+      <c r="D19">
+        <v>25.33416027203955</v>
+      </c>
+      <c r="E19">
+        <v>-6.925</v>
+      </c>
+      <c r="F19">
+        <v>6.375000000000001</v>
+      </c>
+      <c r="G19">
+        <v>12.5</v>
+      </c>
+      <c r="H19">
+        <v>24.2</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>1.94</v>
+      </c>
+      <c r="K19">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L19">
+        <v>1.96</v>
+      </c>
+      <c r="M19">
+        <v>0.3506250000000001</v>
+      </c>
+      <c r="N19">
+        <v>1.609375</v>
+      </c>
+      <c r="O19">
+        <v>0.24140625</v>
+      </c>
+      <c r="P19">
+        <v>1.36796875</v>
+      </c>
+      <c r="Q19">
+        <v>1.34796875</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1036711014002655</v>
+      </c>
+      <c r="T19">
+        <v>0.8796297261969624</v>
+      </c>
+      <c r="U19">
+        <v>0.055</v>
+      </c>
+      <c r="V19">
+        <v>0.15</v>
+      </c>
+      <c r="W19">
+        <v>0.04675</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>5.590017825311942</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09399113625432573</v>
+      </c>
+      <c r="C20">
+        <v>31.08571081920699</v>
+      </c>
+      <c r="D20">
+        <v>25.33571081920699</v>
+      </c>
+      <c r="E20">
+        <v>-6.550000000000001</v>
+      </c>
+      <c r="F20">
+        <v>6.75</v>
+      </c>
+      <c r="G20">
+        <v>12.5</v>
+      </c>
+      <c r="H20">
+        <v>24.2</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>1.94</v>
+      </c>
+      <c r="K20">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L20">
+        <v>1.96</v>
+      </c>
+      <c r="M20">
+        <v>0.37125</v>
+      </c>
+      <c r="N20">
+        <v>1.58875</v>
+      </c>
+      <c r="O20">
+        <v>0.2383125</v>
+      </c>
+      <c r="P20">
+        <v>1.3504375</v>
+      </c>
+      <c r="Q20">
+        <v>1.3304375</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.104361141773568</v>
+      </c>
+      <c r="T20">
+        <v>0.8889864352944035</v>
+      </c>
+      <c r="U20">
+        <v>0.055</v>
+      </c>
+      <c r="V20">
+        <v>0.15</v>
+      </c>
+      <c r="W20">
+        <v>0.04675</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>5.279461279461279</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.0939877583464311</v>
+      </c>
+      <c r="C21">
+        <v>30.71226155618484</v>
+      </c>
+      <c r="D21">
+        <v>25.33726155618484</v>
+      </c>
+      <c r="E21">
+        <v>-6.175000000000001</v>
+      </c>
+      <c r="F21">
+        <v>7.125</v>
+      </c>
+      <c r="G21">
+        <v>12.5</v>
+      </c>
+      <c r="H21">
+        <v>24.2</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1.94</v>
+      </c>
+      <c r="K21">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L21">
+        <v>1.96</v>
+      </c>
+      <c r="M21">
+        <v>0.391875</v>
+      </c>
+      <c r="N21">
+        <v>1.568125</v>
+      </c>
+      <c r="O21">
+        <v>0.23521875</v>
+      </c>
+      <c r="P21">
+        <v>1.33290625</v>
+      </c>
+      <c r="Q21">
+        <v>1.31290625</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1050682201807791</v>
+      </c>
+      <c r="T21">
+        <v>0.8985741742461023</v>
+      </c>
+      <c r="U21">
+        <v>0.055</v>
+      </c>
+      <c r="V21">
+        <v>0.15</v>
+      </c>
+      <c r="W21">
+        <v>0.04675</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>5.001594896331738</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09398438043853645</v>
+      </c>
+      <c r="C22">
+        <v>30.33881248300796</v>
+      </c>
+      <c r="D22">
+        <v>25.33881248300796</v>
+      </c>
+      <c r="E22">
+        <v>-5.800000000000001</v>
+      </c>
+      <c r="F22">
+        <v>7.5</v>
+      </c>
+      <c r="G22">
+        <v>12.5</v>
+      </c>
+      <c r="H22">
+        <v>24.2</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>1.94</v>
+      </c>
+      <c r="K22">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L22">
+        <v>1.96</v>
+      </c>
+      <c r="M22">
+        <v>0.4125</v>
+      </c>
+      <c r="N22">
+        <v>1.5475</v>
+      </c>
+      <c r="O22">
+        <v>0.232125</v>
+      </c>
+      <c r="P22">
+        <v>1.315375</v>
+      </c>
+      <c r="Q22">
+        <v>1.295375</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1057929755481706</v>
+      </c>
+      <c r="T22">
+        <v>0.9084016066715936</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0.15</v>
+      </c>
+      <c r="W22">
+        <v>0.04675</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>4.751515151515152</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09398100253064182</v>
+      </c>
+      <c r="C23">
+        <v>29.9653635997112</v>
+      </c>
+      <c r="D23">
+        <v>25.3403635997112</v>
+      </c>
+      <c r="E23">
+        <v>-5.425000000000001</v>
+      </c>
+      <c r="F23">
+        <v>7.875</v>
+      </c>
+      <c r="G23">
+        <v>12.5</v>
+      </c>
+      <c r="H23">
+        <v>24.2</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>1.94</v>
+      </c>
+      <c r="K23">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L23">
+        <v>1.96</v>
+      </c>
+      <c r="M23">
+        <v>0.433125</v>
+      </c>
+      <c r="N23">
+        <v>1.526875</v>
+      </c>
+      <c r="O23">
+        <v>0.22903125</v>
+      </c>
+      <c r="P23">
+        <v>1.29784375</v>
+      </c>
+      <c r="Q23">
+        <v>1.27784375</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1065360791527111</v>
+      </c>
+      <c r="T23">
+        <v>0.9184778348546924</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0.15</v>
+      </c>
+      <c r="W23">
+        <v>0.04675</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>4.525252525252526</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09468822462274717</v>
+      </c>
+      <c r="C24">
+        <v>29.26970097210639</v>
+      </c>
+      <c r="D24">
+        <v>25.01970097210639</v>
+      </c>
+      <c r="E24">
+        <v>-5.050000000000001</v>
+      </c>
+      <c r="F24">
+        <v>8.25</v>
+      </c>
+      <c r="G24">
+        <v>12.5</v>
+      </c>
+      <c r="H24">
+        <v>24.2</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>1.94</v>
+      </c>
+      <c r="K24">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L24">
+        <v>1.96</v>
+      </c>
+      <c r="M24">
+        <v>0.4851</v>
+      </c>
+      <c r="N24">
+        <v>1.4749</v>
+      </c>
+      <c r="O24">
+        <v>0.221235</v>
+      </c>
+      <c r="P24">
+        <v>1.253665</v>
+      </c>
+      <c r="Q24">
+        <v>1.233665</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1072982366958297</v>
+      </c>
+      <c r="T24">
+        <v>0.9288124278629989</v>
+      </c>
+      <c r="U24">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V24">
+        <v>0.15</v>
+      </c>
+      <c r="W24">
+        <v>0.04998</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>4.04040404040404</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09553824671485253</v>
+      </c>
+      <c r="C25">
+        <v>28.51986918234308</v>
+      </c>
+      <c r="D25">
+        <v>24.64486918234308</v>
+      </c>
+      <c r="E25">
+        <v>-4.675000000000001</v>
+      </c>
+      <c r="F25">
+        <v>8.625</v>
+      </c>
+      <c r="G25">
+        <v>12.5</v>
+      </c>
+      <c r="H25">
+        <v>24.2</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>1.94</v>
+      </c>
+      <c r="K25">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L25">
+        <v>1.96</v>
+      </c>
+      <c r="M25">
+        <v>0.5433750000000001</v>
+      </c>
+      <c r="N25">
+        <v>1.416625</v>
+      </c>
+      <c r="O25">
+        <v>0.21249375</v>
+      </c>
+      <c r="P25">
+        <v>1.20413125</v>
+      </c>
+      <c r="Q25">
+        <v>1.18413125</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1080801905387695</v>
+      </c>
+      <c r="T25">
+        <v>0.9394154518585339</v>
+      </c>
+      <c r="U25">
+        <v>0.063</v>
+      </c>
+      <c r="V25">
+        <v>0.15</v>
+      </c>
+      <c r="W25">
+        <v>0.05355</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>3.607085346215781</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09705126880695789</v>
+      </c>
+      <c r="C26">
+        <v>27.50474181183888</v>
+      </c>
+      <c r="D26">
+        <v>24.00474181183888</v>
+      </c>
+      <c r="E26">
+        <v>-4.300000000000001</v>
+      </c>
+      <c r="F26">
+        <v>9</v>
+      </c>
+      <c r="G26">
+        <v>12.5</v>
+      </c>
+      <c r="H26">
+        <v>24.2</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>1.94</v>
+      </c>
+      <c r="K26">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L26">
+        <v>1.96</v>
+      </c>
+      <c r="M26">
+        <v>0.6309</v>
+      </c>
+      <c r="N26">
+        <v>1.3291</v>
+      </c>
+      <c r="O26">
+        <v>0.199365</v>
+      </c>
+      <c r="P26">
+        <v>1.129735</v>
+      </c>
+      <c r="Q26">
+        <v>1.109735</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1088827221144183</v>
+      </c>
+      <c r="T26">
+        <v>0.95029750280132</v>
+      </c>
+      <c r="U26">
+        <v>0.0701</v>
+      </c>
+      <c r="V26">
+        <v>0.15</v>
+      </c>
+      <c r="W26">
+        <v>0.05958499999999999</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>3.10667300681566</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1017024908990632</v>
+      </c>
+      <c r="C27">
+        <v>25.35475033161798</v>
+      </c>
+      <c r="D27">
+        <v>22.22975033161798</v>
+      </c>
+      <c r="E27">
+        <v>-3.925000000000001</v>
+      </c>
+      <c r="F27">
+        <v>9.375</v>
+      </c>
+      <c r="G27">
+        <v>12.5</v>
+      </c>
+      <c r="H27">
+        <v>24.2</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>1.94</v>
+      </c>
+      <c r="K27">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L27">
+        <v>1.96</v>
+      </c>
+      <c r="M27">
+        <v>0.8568750000000001</v>
+      </c>
+      <c r="N27">
+        <v>1.103125</v>
+      </c>
+      <c r="O27">
+        <v>0.16546875</v>
+      </c>
+      <c r="P27">
+        <v>0.9376562499999999</v>
+      </c>
+      <c r="Q27">
+        <v>0.9176562499999998</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1097066545320843</v>
+      </c>
+      <c r="T27">
+        <v>0.9614697417692468</v>
+      </c>
+      <c r="U27">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V27">
+        <v>0.15</v>
+      </c>
+      <c r="W27">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>2.287381473377097</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1020085129911686</v>
+      </c>
+      <c r="C28">
+        <v>24.87212567187615</v>
+      </c>
+      <c r="D28">
+        <v>22.12212567187615</v>
+      </c>
+      <c r="E28">
+        <v>-3.550000000000001</v>
+      </c>
+      <c r="F28">
+        <v>9.75</v>
+      </c>
+      <c r="G28">
+        <v>12.5</v>
+      </c>
+      <c r="H28">
+        <v>24.2</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>1.94</v>
+      </c>
+      <c r="K28">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L28">
+        <v>1.96</v>
+      </c>
+      <c r="M28">
+        <v>0.8911500000000001</v>
+      </c>
+      <c r="N28">
+        <v>1.06885</v>
+      </c>
+      <c r="O28">
+        <v>0.1603275</v>
+      </c>
+      <c r="P28">
+        <v>0.9085224999999999</v>
+      </c>
+      <c r="Q28">
+        <v>0.8885224999999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1105528553934711</v>
+      </c>
+      <c r="T28">
+        <v>0.9729439331417125</v>
+      </c>
+      <c r="U28">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0.15</v>
+      </c>
+      <c r="W28">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>2.199405262862593</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.102314535083274</v>
+      </c>
+      <c r="C29">
+        <v>24.39053811406675</v>
+      </c>
+      <c r="D29">
+        <v>22.01553811406675</v>
+      </c>
+      <c r="E29">
+        <v>-3.175000000000001</v>
+      </c>
+      <c r="F29">
+        <v>10.125</v>
+      </c>
+      <c r="G29">
+        <v>12.5</v>
+      </c>
+      <c r="H29">
+        <v>24.2</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>1.94</v>
+      </c>
+      <c r="K29">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L29">
+        <v>1.96</v>
+      </c>
+      <c r="M29">
+        <v>0.9254250000000001</v>
+      </c>
+      <c r="N29">
+        <v>1.034575</v>
+      </c>
+      <c r="O29">
+        <v>0.15518625</v>
+      </c>
+      <c r="P29">
+        <v>0.8793887499999998</v>
+      </c>
+      <c r="Q29">
+        <v>0.8593887499999998</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1114222398401013</v>
+      </c>
+      <c r="T29">
+        <v>0.984732485921643</v>
+      </c>
+      <c r="U29">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0.15</v>
+      </c>
+      <c r="W29">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>2.117945808682497</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1026205571753793</v>
+      </c>
+      <c r="C30">
+        <v>23.90997273935563</v>
+      </c>
+      <c r="D30">
+        <v>21.90997273935563</v>
+      </c>
+      <c r="E30">
+        <v>-2.799999999999999</v>
+      </c>
+      <c r="F30">
+        <v>10.5</v>
+      </c>
+      <c r="G30">
+        <v>12.5</v>
+      </c>
+      <c r="H30">
+        <v>24.2</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>1.94</v>
+      </c>
+      <c r="K30">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L30">
+        <v>1.96</v>
+      </c>
+      <c r="M30">
+        <v>0.9597000000000002</v>
+      </c>
+      <c r="N30">
+        <v>1.0003</v>
+      </c>
+      <c r="O30">
+        <v>0.150045</v>
+      </c>
+      <c r="P30">
+        <v>0.8502549999999998</v>
+      </c>
+      <c r="Q30">
+        <v>0.8302549999999997</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1123157738546935</v>
+      </c>
+      <c r="T30">
+        <v>0.9968484985010159</v>
+      </c>
+      <c r="U30">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V30">
+        <v>0.15</v>
+      </c>
+      <c r="W30">
+        <v>0.07769000000000001</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>2.042304886943836</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1081277292674847</v>
+      </c>
+      <c r="C31">
+        <v>21.79451489249001</v>
+      </c>
+      <c r="D31">
+        <v>20.16951489249001</v>
+      </c>
+      <c r="E31">
+        <v>-2.425000000000001</v>
+      </c>
+      <c r="F31">
+        <v>10.875</v>
+      </c>
+      <c r="G31">
+        <v>12.5</v>
+      </c>
+      <c r="H31">
+        <v>24.2</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>1.94</v>
+      </c>
+      <c r="K31">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L31">
+        <v>1.96</v>
+      </c>
+      <c r="M31">
+        <v>1.2234375</v>
+      </c>
+      <c r="N31">
+        <v>0.7365625</v>
+      </c>
+      <c r="O31">
+        <v>0.110484375</v>
+      </c>
+      <c r="P31">
+        <v>0.626078125</v>
+      </c>
+      <c r="Q31">
+        <v>0.606078125</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1132344778415277</v>
+      </c>
+      <c r="T31">
+        <v>1.009305807209385</v>
+      </c>
+      <c r="U31">
+        <v>0.1125</v>
+      </c>
+      <c r="V31">
+        <v>0.15</v>
+      </c>
+      <c r="W31">
+        <v>0.095625</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>1.602043422733078</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.10861310135959</v>
+      </c>
+      <c r="C32">
+        <v>21.27928734995908</v>
+      </c>
+      <c r="D32">
+        <v>20.02928734995908</v>
+      </c>
+      <c r="E32">
+        <v>-2.050000000000001</v>
+      </c>
+      <c r="F32">
+        <v>11.25</v>
+      </c>
+      <c r="G32">
+        <v>12.5</v>
+      </c>
+      <c r="H32">
+        <v>24.2</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>1.94</v>
+      </c>
+      <c r="K32">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L32">
+        <v>1.96</v>
+      </c>
+      <c r="M32">
+        <v>1.265625</v>
+      </c>
+      <c r="N32">
+        <v>0.694375</v>
+      </c>
+      <c r="O32">
+        <v>0.10415625</v>
+      </c>
+      <c r="P32">
+        <v>0.59021875</v>
+      </c>
+      <c r="Q32">
+        <v>0.57021875</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1141794305137</v>
+      </c>
+      <c r="T32">
+        <v>1.022119039023708</v>
+      </c>
+      <c r="U32">
+        <v>0.1125</v>
+      </c>
+      <c r="V32">
+        <v>0.15</v>
+      </c>
+      <c r="W32">
+        <v>0.095625</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>1.548641975308642</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1329266059484334</v>
+      </c>
+      <c r="C33">
+        <v>15.73059426937268</v>
+      </c>
+      <c r="D33">
+        <v>14.85559426937268</v>
+      </c>
+      <c r="E33">
+        <v>-1.675000000000001</v>
+      </c>
+      <c r="F33">
+        <v>11.625</v>
+      </c>
+      <c r="G33">
+        <v>12.5</v>
+      </c>
+      <c r="H33">
+        <v>24.2</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>1.94</v>
+      </c>
+      <c r="K33">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L33">
+        <v>1.96</v>
+      </c>
+      <c r="M33">
+        <v>2.285475</v>
+      </c>
+      <c r="N33">
+        <v>-0.325475</v>
+      </c>
+      <c r="O33">
+        <v>-0.04882125</v>
+      </c>
+      <c r="P33">
+        <v>-0.27665375</v>
+      </c>
+      <c r="Q33">
+        <v>-0.29665375</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1156820376064252</v>
+      </c>
+      <c r="T33">
+        <v>1.042493872147013</v>
+      </c>
+      <c r="U33">
+        <v>0.1966</v>
+      </c>
+      <c r="V33">
+        <v>0.1286384668394973</v>
+      </c>
+      <c r="W33">
+        <v>0.1713096774193548</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.8575897789299818</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1345046059484334</v>
+      </c>
+      <c r="C34">
+        <v>15.11065174518842</v>
+      </c>
+      <c r="D34">
+        <v>14.61065174518842</v>
+      </c>
+      <c r="E34">
+        <v>-1.300000000000001</v>
+      </c>
+      <c r="F34">
+        <v>12</v>
+      </c>
+      <c r="G34">
+        <v>12.5</v>
+      </c>
+      <c r="H34">
+        <v>24.2</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>1.94</v>
+      </c>
+      <c r="K34">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L34">
+        <v>1.96</v>
+      </c>
+      <c r="M34">
+        <v>2.3592</v>
+      </c>
+      <c r="N34">
+        <v>-0.3992</v>
+      </c>
+      <c r="O34">
+        <v>-0.05988000000000001</v>
+      </c>
+      <c r="P34">
+        <v>-0.33932</v>
+      </c>
+      <c r="Q34">
+        <v>-0.35932</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1168126558065197</v>
+      </c>
+      <c r="T34">
+        <v>1.05782466438447</v>
+      </c>
+      <c r="U34">
+        <v>0.1966</v>
+      </c>
+      <c r="V34">
+        <v>0.124618514750763</v>
+      </c>
+      <c r="W34">
+        <v>0.1721</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.8307900983384198</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1360826059484334</v>
+      </c>
+      <c r="C35">
+        <v>14.49865553986341</v>
+      </c>
+      <c r="D35">
+        <v>14.37365553986341</v>
+      </c>
+      <c r="E35">
+        <v>-0.9250000000000007</v>
+      </c>
+      <c r="F35">
+        <v>12.375</v>
+      </c>
+      <c r="G35">
+        <v>12.5</v>
+      </c>
+      <c r="H35">
+        <v>24.2</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>1.94</v>
+      </c>
+      <c r="K35">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L35">
+        <v>1.96</v>
+      </c>
+      <c r="M35">
+        <v>2.432925</v>
+      </c>
+      <c r="N35">
+        <v>-0.472925</v>
+      </c>
+      <c r="O35">
+        <v>-0.07093875000000002</v>
+      </c>
+      <c r="P35">
+        <v>-0.40198625</v>
+      </c>
+      <c r="Q35">
+        <v>-0.42198625</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1179770238036319</v>
+      </c>
+      <c r="T35">
+        <v>1.073613092211103</v>
+      </c>
+      <c r="U35">
+        <v>0.1966</v>
+      </c>
+      <c r="V35">
+        <v>0.120842196121952</v>
+      </c>
+      <c r="W35">
+        <v>0.1728424242424242</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.8056146408130131</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1436858618957932</v>
+      </c>
+      <c r="C36">
+        <v>13.081698311373</v>
+      </c>
+      <c r="D36">
+        <v>13.331698311373</v>
+      </c>
+      <c r="E36">
+        <v>-0.5499999999999989</v>
+      </c>
+      <c r="F36">
+        <v>12.75</v>
+      </c>
+      <c r="G36">
+        <v>12.5</v>
+      </c>
+      <c r="H36">
+        <v>24.2</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>1.94</v>
+      </c>
+      <c r="K36">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L36">
+        <v>1.96</v>
+      </c>
+      <c r="M36">
+        <v>2.72595</v>
+      </c>
+      <c r="N36">
+        <v>-0.7659500000000001</v>
+      </c>
+      <c r="O36">
+        <v>-0.1148925</v>
+      </c>
+      <c r="P36">
+        <v>-0.6510575000000001</v>
+      </c>
+      <c r="Q36">
+        <v>-0.6710575000000001</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1194452452966563</v>
+      </c>
+      <c r="T36">
+        <v>1.093521668480479</v>
+      </c>
+      <c r="U36">
+        <v>0.2138</v>
+      </c>
+      <c r="V36">
+        <v>0.1078523083695593</v>
+      </c>
+      <c r="W36">
+        <v>0.1907411764705882</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.7190153891303949</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1454358618957932</v>
+      </c>
+      <c r="C37">
+        <v>12.48791195160501</v>
+      </c>
+      <c r="D37">
+        <v>13.11291195160501</v>
+      </c>
+      <c r="E37">
+        <v>-0.1749999999999989</v>
+      </c>
+      <c r="F37">
+        <v>13.125</v>
+      </c>
+      <c r="G37">
+        <v>12.5</v>
+      </c>
+      <c r="H37">
+        <v>24.2</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>1.94</v>
+      </c>
+      <c r="K37">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L37">
+        <v>1.96</v>
+      </c>
+      <c r="M37">
+        <v>2.806125</v>
+      </c>
+      <c r="N37">
+        <v>-0.8461250000000002</v>
+      </c>
+      <c r="O37">
+        <v>-0.1269187500000001</v>
+      </c>
+      <c r="P37">
+        <v>-0.7192062500000002</v>
+      </c>
+      <c r="Q37">
+        <v>-0.7392062500000002</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1206859413781434</v>
+      </c>
+      <c r="T37">
+        <v>1.110345078764794</v>
+      </c>
+      <c r="U37">
+        <v>0.2138</v>
+      </c>
+      <c r="V37">
+        <v>0.1047708138447147</v>
+      </c>
+      <c r="W37">
+        <v>0.1914</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.6984720922980978</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1471858618957932</v>
+      </c>
+      <c r="C38">
+        <v>11.90119064853163</v>
+      </c>
+      <c r="D38">
+        <v>12.90119064853163</v>
+      </c>
+      <c r="E38">
+        <v>0.1999999999999993</v>
+      </c>
+      <c r="F38">
+        <v>13.5</v>
+      </c>
+      <c r="G38">
+        <v>12.5</v>
+      </c>
+      <c r="H38">
+        <v>24.2</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>1.94</v>
+      </c>
+      <c r="K38">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L38">
+        <v>1.96</v>
+      </c>
+      <c r="M38">
+        <v>2.8863</v>
+      </c>
+      <c r="N38">
+        <v>-0.9262999999999999</v>
+      </c>
+      <c r="O38">
+        <v>-0.138945</v>
+      </c>
+      <c r="P38">
+        <v>-0.7873549999999999</v>
+      </c>
+      <c r="Q38">
+        <v>-0.8073549999999999</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1219654092121769</v>
+      </c>
+      <c r="T38">
+        <v>1.127694220620494</v>
+      </c>
+      <c r="U38">
+        <v>0.2138</v>
+      </c>
+      <c r="V38">
+        <v>0.1018605134601393</v>
+      </c>
+      <c r="W38">
+        <v>0.1920222222222222</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.6790700897342619</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1489358618957932</v>
+      </c>
+      <c r="C39">
+        <v>11.3211976222248</v>
+      </c>
+      <c r="D39">
+        <v>12.6961976222248</v>
+      </c>
+      <c r="E39">
+        <v>0.5749999999999993</v>
+      </c>
+      <c r="F39">
+        <v>13.875</v>
+      </c>
+      <c r="G39">
+        <v>12.5</v>
+      </c>
+      <c r="H39">
+        <v>24.2</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>1.94</v>
+      </c>
+      <c r="K39">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L39">
+        <v>1.96</v>
+      </c>
+      <c r="M39">
+        <v>2.966475</v>
+      </c>
+      <c r="N39">
+        <v>-1.006475</v>
+      </c>
+      <c r="O39">
+        <v>-0.15097125</v>
+      </c>
+      <c r="P39">
+        <v>-0.85550375</v>
+      </c>
+      <c r="Q39">
+        <v>-0.87550375</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1232854950726876</v>
+      </c>
+      <c r="T39">
+        <v>1.145594128884311</v>
+      </c>
+      <c r="U39">
+        <v>0.2138</v>
+      </c>
+      <c r="V39">
+        <v>0.09910752660986526</v>
+      </c>
+      <c r="W39">
+        <v>0.1926108108108108</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.6607168440657682</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1506858618957932</v>
+      </c>
+      <c r="C40">
+        <v>10.74761716297439</v>
+      </c>
+      <c r="D40">
+        <v>12.49761716297439</v>
+      </c>
+      <c r="E40">
+        <v>0.9499999999999993</v>
+      </c>
+      <c r="F40">
+        <v>14.25</v>
+      </c>
+      <c r="G40">
+        <v>12.5</v>
+      </c>
+      <c r="H40">
+        <v>24.2</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>1.94</v>
+      </c>
+      <c r="K40">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L40">
+        <v>1.96</v>
+      </c>
+      <c r="M40">
+        <v>3.04665</v>
+      </c>
+      <c r="N40">
+        <v>-1.08665</v>
+      </c>
+      <c r="O40">
+        <v>-0.1629975</v>
+      </c>
+      <c r="P40">
+        <v>-0.9236524999999998</v>
+      </c>
+      <c r="Q40">
+        <v>-0.9436524999999998</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1246481643480535</v>
+      </c>
+      <c r="T40">
+        <v>1.164071453543736</v>
+      </c>
+      <c r="U40">
+        <v>0.2138</v>
+      </c>
+      <c r="V40">
+        <v>0.0964994338043425</v>
+      </c>
+      <c r="W40">
+        <v>0.1931684210526315</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.6433295586956166</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1524358618957932</v>
+      </c>
+      <c r="C41">
+        <v>10.18015300887433</v>
+      </c>
+      <c r="D41">
+        <v>12.30515300887433</v>
+      </c>
+      <c r="E41">
+        <v>1.324999999999999</v>
+      </c>
+      <c r="F41">
+        <v>14.625</v>
+      </c>
+      <c r="G41">
+        <v>12.5</v>
+      </c>
+      <c r="H41">
+        <v>24.2</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>1.94</v>
+      </c>
+      <c r="K41">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L41">
+        <v>1.96</v>
+      </c>
+      <c r="M41">
+        <v>3.126825</v>
+      </c>
+      <c r="N41">
+        <v>-1.166825</v>
+      </c>
+      <c r="O41">
+        <v>-0.17502375</v>
+      </c>
+      <c r="P41">
+        <v>-0.9918012499999997</v>
+      </c>
+      <c r="Q41">
+        <v>-1.01180125</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.126055511304579</v>
+      </c>
+      <c r="T41">
+        <v>1.18315459212642</v>
+      </c>
+      <c r="U41">
+        <v>0.2138</v>
+      </c>
+      <c r="V41">
+        <v>0.09402508934782089</v>
+      </c>
+      <c r="W41">
+        <v>0.1936974358974359</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.6268339289854725</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1541858618957932</v>
+      </c>
+      <c r="C42">
+        <v>9.618526871046651</v>
+      </c>
+      <c r="D42">
+        <v>12.11852687104665</v>
+      </c>
+      <c r="E42">
+        <v>1.699999999999999</v>
+      </c>
+      <c r="F42">
+        <v>15</v>
+      </c>
+      <c r="G42">
+        <v>12.5</v>
+      </c>
+      <c r="H42">
+        <v>24.2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1.94</v>
+      </c>
+      <c r="K42">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L42">
+        <v>1.96</v>
+      </c>
+      <c r="M42">
+        <v>3.207</v>
+      </c>
+      <c r="N42">
+        <v>-1.247</v>
+      </c>
+      <c r="O42">
+        <v>-0.18705</v>
+      </c>
+      <c r="P42">
+        <v>-1.05995</v>
+      </c>
+      <c r="Q42">
+        <v>-1.07995</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.127509769826322</v>
+      </c>
+      <c r="T42">
+        <v>1.202873835328527</v>
+      </c>
+      <c r="U42">
+        <v>0.2138</v>
+      </c>
+      <c r="V42">
+        <v>0.09167446211412537</v>
+      </c>
+      <c r="W42">
+        <v>0.1942</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.6111630807608357</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1559358618957932</v>
+      </c>
+      <c r="C43">
+        <v>9.062477091063828</v>
+      </c>
+      <c r="D43">
+        <v>11.93747709106383</v>
+      </c>
+      <c r="E43">
+        <v>2.075000000000001</v>
+      </c>
+      <c r="F43">
+        <v>15.375</v>
+      </c>
+      <c r="G43">
+        <v>12.5</v>
+      </c>
+      <c r="H43">
+        <v>24.2</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1.94</v>
+      </c>
+      <c r="K43">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L43">
+        <v>1.96</v>
+      </c>
+      <c r="M43">
+        <v>3.287175</v>
+      </c>
+      <c r="N43">
+        <v>-1.327175</v>
+      </c>
+      <c r="O43">
+        <v>-0.1990762500000001</v>
+      </c>
+      <c r="P43">
+        <v>-1.12809875</v>
+      </c>
+      <c r="Q43">
+        <v>-1.14809875</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1290133252471071</v>
+      </c>
+      <c r="T43">
+        <v>1.223261527452739</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0.08943849962353694</v>
+      </c>
+      <c r="W43">
+        <v>0.1946780487804878</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.5962566641569127</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1576858618957932</v>
+      </c>
+      <c r="C44">
+        <v>8.511757416947553</v>
+      </c>
+      <c r="D44">
+        <v>11.76175741694755</v>
+      </c>
+      <c r="E44">
+        <v>2.449999999999999</v>
+      </c>
+      <c r="F44">
+        <v>15.75</v>
+      </c>
+      <c r="G44">
+        <v>12.5</v>
+      </c>
+      <c r="H44">
+        <v>24.2</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1.94</v>
+      </c>
+      <c r="K44">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L44">
+        <v>1.96</v>
+      </c>
+      <c r="M44">
+        <v>3.36735</v>
+      </c>
+      <c r="N44">
+        <v>-1.40735</v>
+      </c>
+      <c r="O44">
+        <v>-0.2111025000000001</v>
+      </c>
+      <c r="P44">
+        <v>-1.1962475</v>
+      </c>
+      <c r="Q44">
+        <v>-1.2162475</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.13056872740654</v>
+      </c>
+      <c r="T44">
+        <v>1.244352243443304</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0.08730901153726224</v>
+      </c>
+      <c r="W44">
+        <v>0.1951333333333333</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.5820600769150815</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1594358618957932</v>
+      </c>
+      <c r="C45">
+        <v>7.966135885703068</v>
+      </c>
+      <c r="D45">
+        <v>11.59113588570307</v>
+      </c>
+      <c r="E45">
+        <v>2.824999999999999</v>
+      </c>
+      <c r="F45">
+        <v>16.125</v>
+      </c>
+      <c r="G45">
+        <v>12.5</v>
+      </c>
+      <c r="H45">
+        <v>24.2</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1.94</v>
+      </c>
+      <c r="K45">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L45">
+        <v>1.96</v>
+      </c>
+      <c r="M45">
+        <v>3.447525</v>
+      </c>
+      <c r="N45">
+        <v>-1.487525</v>
+      </c>
+      <c r="O45">
+        <v>-0.22312875</v>
+      </c>
+      <c r="P45">
+        <v>-1.26439625</v>
+      </c>
+      <c r="Q45">
+        <v>-1.28439625</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1321787050803389</v>
+      </c>
+      <c r="T45">
+        <v>1.266182984556344</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0.08527856940848871</v>
+      </c>
+      <c r="W45">
+        <v>0.1955674418604651</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.5685237960565914</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1611858618957932</v>
+      </c>
+      <c r="C46">
+        <v>7.425393801725654</v>
+      </c>
+      <c r="D46">
+        <v>11.42539380172566</v>
+      </c>
+      <c r="E46">
+        <v>3.199999999999999</v>
+      </c>
+      <c r="F46">
+        <v>16.5</v>
+      </c>
+      <c r="G46">
+        <v>12.5</v>
+      </c>
+      <c r="H46">
+        <v>24.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1.94</v>
+      </c>
+      <c r="K46">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L46">
+        <v>1.96</v>
+      </c>
+      <c r="M46">
+        <v>3.5277</v>
+      </c>
+      <c r="N46">
+        <v>-1.5677</v>
+      </c>
+      <c r="O46">
+        <v>-0.235155</v>
+      </c>
+      <c r="P46">
+        <v>-1.332545</v>
+      </c>
+      <c r="Q46">
+        <v>-1.352545</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1338461819567736</v>
+      </c>
+      <c r="T46">
+        <v>1.28879339499485</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0.08334042010375033</v>
+      </c>
+      <c r="W46">
+        <v>0.1959818181818182</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.5556028006916688</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1629358618957932</v>
+      </c>
+      <c r="C47">
+        <v>6.889324801618301</v>
+      </c>
+      <c r="D47">
+        <v>11.2643248016183</v>
+      </c>
+      <c r="E47">
+        <v>3.574999999999999</v>
+      </c>
+      <c r="F47">
+        <v>16.875</v>
+      </c>
+      <c r="G47">
+        <v>12.5</v>
+      </c>
+      <c r="H47">
+        <v>24.2</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1.94</v>
+      </c>
+      <c r="K47">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L47">
+        <v>1.96</v>
+      </c>
+      <c r="M47">
+        <v>3.607875</v>
+      </c>
+      <c r="N47">
+        <v>-1.647875</v>
+      </c>
+      <c r="O47">
+        <v>-0.24718125</v>
+      </c>
+      <c r="P47">
+        <v>-1.40069375</v>
+      </c>
+      <c r="Q47">
+        <v>-1.42069375</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1355742943559876</v>
+      </c>
+      <c r="T47">
+        <v>1.312226002176575</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0.08148841076811145</v>
+      </c>
+      <c r="W47">
+        <v>0.1963777777777778</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.5432560717874095</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1646858618957932</v>
+      </c>
+      <c r="C48">
+        <v>6.357733997011906</v>
+      </c>
+      <c r="D48">
+        <v>11.1077339970119</v>
+      </c>
+      <c r="E48">
+        <v>3.949999999999999</v>
+      </c>
+      <c r="F48">
+        <v>17.25</v>
+      </c>
+      <c r="G48">
+        <v>12.5</v>
+      </c>
+      <c r="H48">
+        <v>24.2</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1.94</v>
+      </c>
+      <c r="K48">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L48">
+        <v>1.96</v>
+      </c>
+      <c r="M48">
+        <v>3.68805</v>
+      </c>
+      <c r="N48">
+        <v>-1.72805</v>
+      </c>
+      <c r="O48">
+        <v>-0.2592075</v>
+      </c>
+      <c r="P48">
+        <v>-1.4688425</v>
+      </c>
+      <c r="Q48">
+        <v>-1.4888425</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1373664109181356</v>
+      </c>
+      <c r="T48">
+        <v>1.336526483698363</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0.07971692357750032</v>
+      </c>
+      <c r="W48">
+        <v>0.1967565217391304</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.5314461571833354</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1664358618957932</v>
+      </c>
+      <c r="C49">
+        <v>5.830437187901616</v>
+      </c>
+      <c r="D49">
+        <v>10.95543718790162</v>
+      </c>
+      <c r="E49">
+        <v>4.324999999999999</v>
+      </c>
+      <c r="F49">
+        <v>17.625</v>
+      </c>
+      <c r="G49">
+        <v>12.5</v>
+      </c>
+      <c r="H49">
+        <v>24.2</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1.94</v>
+      </c>
+      <c r="K49">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L49">
+        <v>1.96</v>
+      </c>
+      <c r="M49">
+        <v>3.768225</v>
+      </c>
+      <c r="N49">
+        <v>-1.808225</v>
+      </c>
+      <c r="O49">
+        <v>-0.27123375</v>
+      </c>
+      <c r="P49">
+        <v>-1.53699125</v>
+      </c>
+      <c r="Q49">
+        <v>-1.55699125</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1392261545203645</v>
+      </c>
+      <c r="T49">
+        <v>1.361743964522861</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0.07802081882053222</v>
+      </c>
+      <c r="W49">
+        <v>0.1971191489361702</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.5201387921368814</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1681858618957932</v>
+      </c>
+      <c r="C50">
+        <v>5.307260139822986</v>
+      </c>
+      <c r="D50">
+        <v>10.80726013982299</v>
+      </c>
+      <c r="E50">
+        <v>4.699999999999999</v>
+      </c>
+      <c r="F50">
+        <v>18</v>
+      </c>
+      <c r="G50">
+        <v>12.5</v>
+      </c>
+      <c r="H50">
+        <v>24.2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1.94</v>
+      </c>
+      <c r="K50">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L50">
+        <v>1.96</v>
+      </c>
+      <c r="M50">
+        <v>3.8484</v>
+      </c>
+      <c r="N50">
+        <v>-1.8884</v>
+      </c>
+      <c r="O50">
+        <v>-0.28326</v>
+      </c>
+      <c r="P50">
+        <v>-1.60514</v>
+      </c>
+      <c r="Q50">
+        <v>-1.62514</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1411574267226792</v>
+      </c>
+      <c r="T50">
+        <v>1.387931348455993</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0.07639538509510448</v>
+      </c>
+      <c r="W50">
+        <v>0.1974666666666667</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.5093025673006963</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1823979721031462</v>
+      </c>
+      <c r="C51">
+        <v>3.862649128628682</v>
+      </c>
+      <c r="D51">
+        <v>9.73764912862868</v>
+      </c>
+      <c r="E51">
+        <v>5.074999999999999</v>
+      </c>
+      <c r="F51">
+        <v>18.375</v>
+      </c>
+      <c r="G51">
+        <v>12.5</v>
+      </c>
+      <c r="H51">
+        <v>24.2</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1.94</v>
+      </c>
+      <c r="K51">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L51">
+        <v>1.96</v>
+      </c>
+      <c r="M51">
+        <v>4.38795</v>
+      </c>
+      <c r="N51">
+        <v>-2.42795</v>
+      </c>
+      <c r="O51">
+        <v>-0.3641925000000001</v>
+      </c>
+      <c r="P51">
+        <v>-2.0637575</v>
+      </c>
+      <c r="Q51">
+        <v>-2.0837575</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1435803374571494</v>
+      </c>
+      <c r="T51">
+        <v>1.420785181055681</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.06700167504187605</v>
+      </c>
+      <c r="W51">
+        <v>0.2228</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.446677833612507</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1843979721031462</v>
+      </c>
+      <c r="C52">
+        <v>3.353888349024825</v>
+      </c>
+      <c r="D52">
+        <v>9.603888349024825</v>
+      </c>
+      <c r="E52">
+        <v>5.449999999999999</v>
+      </c>
+      <c r="F52">
+        <v>18.75</v>
+      </c>
+      <c r="G52">
+        <v>12.5</v>
+      </c>
+      <c r="H52">
+        <v>24.2</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1.94</v>
+      </c>
+      <c r="K52">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L52">
+        <v>1.96</v>
+      </c>
+      <c r="M52">
+        <v>4.4775</v>
+      </c>
+      <c r="N52">
+        <v>-2.5175</v>
+      </c>
+      <c r="O52">
+        <v>-0.377625</v>
+      </c>
+      <c r="P52">
+        <v>-2.139875</v>
+      </c>
+      <c r="Q52">
+        <v>-2.159875</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1456759442062925</v>
+      </c>
+      <c r="T52">
+        <v>1.449200884676795</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.06566164154103853</v>
+      </c>
+      <c r="W52">
+        <v>0.22312</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.4377442769402569</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1863979721031462</v>
+      </c>
+      <c r="C53">
+        <v>2.848752572602187</v>
+      </c>
+      <c r="D53">
+        <v>9.473752572602187</v>
+      </c>
+      <c r="E53">
+        <v>5.824999999999999</v>
+      </c>
+      <c r="F53">
+        <v>19.125</v>
+      </c>
+      <c r="G53">
+        <v>12.5</v>
+      </c>
+      <c r="H53">
+        <v>24.2</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1.94</v>
+      </c>
+      <c r="K53">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L53">
+        <v>1.96</v>
+      </c>
+      <c r="M53">
+        <v>4.56705</v>
+      </c>
+      <c r="N53">
+        <v>-2.60705</v>
+      </c>
+      <c r="O53">
+        <v>-0.3910575000000001</v>
+      </c>
+      <c r="P53">
+        <v>-2.2159925</v>
+      </c>
+      <c r="Q53">
+        <v>-2.2359925</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1478570859247882</v>
+      </c>
+      <c r="T53">
+        <v>1.478776412935505</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.06437415837356719</v>
+      </c>
+      <c r="W53">
+        <v>0.2234274509803922</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.4291610558237812</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1883979721031462</v>
+      </c>
+      <c r="C54">
+        <v>2.347096409561821</v>
+      </c>
+      <c r="D54">
+        <v>9.34709640956182</v>
+      </c>
+      <c r="E54">
+        <v>6.199999999999999</v>
+      </c>
+      <c r="F54">
+        <v>19.5</v>
+      </c>
+      <c r="G54">
+        <v>12.5</v>
+      </c>
+      <c r="H54">
+        <v>24.2</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1.94</v>
+      </c>
+      <c r="K54">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L54">
+        <v>1.96</v>
+      </c>
+      <c r="M54">
+        <v>4.6566</v>
+      </c>
+      <c r="N54">
+        <v>-2.6966</v>
+      </c>
+      <c r="O54">
+        <v>-0.4044900000000001</v>
+      </c>
+      <c r="P54">
+        <v>-2.29211</v>
+      </c>
+      <c r="Q54">
+        <v>-2.31211</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1501291085482213</v>
+      </c>
+      <c r="T54">
+        <v>1.509584254871662</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.06313619378946013</v>
+      </c>
+      <c r="W54">
+        <v>0.2237230769230769</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.4209079585964008</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1903979721031462</v>
+      </c>
+      <c r="C55">
+        <v>1.848782142492311</v>
+      </c>
+      <c r="D55">
+        <v>9.223782142492309</v>
+      </c>
+      <c r="E55">
+        <v>6.574999999999999</v>
+      </c>
+      <c r="F55">
+        <v>19.875</v>
+      </c>
+      <c r="G55">
+        <v>12.5</v>
+      </c>
+      <c r="H55">
+        <v>24.2</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1.94</v>
+      </c>
+      <c r="K55">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L55">
+        <v>1.96</v>
+      </c>
+      <c r="M55">
+        <v>4.74615</v>
+      </c>
+      <c r="N55">
+        <v>-2.78615</v>
+      </c>
+      <c r="O55">
+        <v>-0.4179225000000001</v>
+      </c>
+      <c r="P55">
+        <v>-2.3682275</v>
+      </c>
+      <c r="Q55">
+        <v>-2.3882275</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1524978129854175</v>
+      </c>
+      <c r="T55">
+        <v>1.541703068805101</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.06194494485003636</v>
+      </c>
+      <c r="W55">
+        <v>0.2240075471698113</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.4129662990002423</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1923979721031462</v>
+      </c>
+      <c r="C56">
+        <v>1.353679226858787</v>
+      </c>
+      <c r="D56">
+        <v>9.103679226858786</v>
+      </c>
+      <c r="E56">
+        <v>6.949999999999999</v>
+      </c>
+      <c r="F56">
+        <v>20.25</v>
+      </c>
+      <c r="G56">
+        <v>12.5</v>
+      </c>
+      <c r="H56">
+        <v>24.2</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1.94</v>
+      </c>
+      <c r="K56">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L56">
+        <v>1.96</v>
+      </c>
+      <c r="M56">
+        <v>4.8357</v>
+      </c>
+      <c r="N56">
+        <v>-2.8757</v>
+      </c>
+      <c r="O56">
+        <v>-0.4313550000000001</v>
+      </c>
+      <c r="P56">
+        <v>-2.444345</v>
+      </c>
+      <c r="Q56">
+        <v>-2.464345</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.154969504572057</v>
+      </c>
+      <c r="T56">
+        <v>1.57521835290956</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.06079781624170235</v>
+      </c>
+      <c r="W56">
+        <v>0.2242814814814815</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.4053187749446823</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1943979721031462</v>
+      </c>
+      <c r="C57">
+        <v>0.8616638300151287</v>
+      </c>
+      <c r="D57">
+        <v>8.986663830015129</v>
+      </c>
+      <c r="E57">
+        <v>7.324999999999999</v>
+      </c>
+      <c r="F57">
+        <v>20.625</v>
+      </c>
+      <c r="G57">
+        <v>12.5</v>
+      </c>
+      <c r="H57">
+        <v>24.2</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1.94</v>
+      </c>
+      <c r="K57">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L57">
+        <v>1.96</v>
+      </c>
+      <c r="M57">
+        <v>4.92525</v>
+      </c>
+      <c r="N57">
+        <v>-2.96525</v>
+      </c>
+      <c r="O57">
+        <v>-0.4447875000000001</v>
+      </c>
+      <c r="P57">
+        <v>-2.5204625</v>
+      </c>
+      <c r="Q57">
+        <v>-2.5404625</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1575510491181027</v>
+      </c>
+      <c r="T57">
+        <v>1.610223205196439</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.05969240140094412</v>
+      </c>
+      <c r="W57">
+        <v>0.2245454545454545</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.3979493426729608</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1963979721031462</v>
+      </c>
+      <c r="C58">
+        <v>0.3726184053172368</v>
+      </c>
+      <c r="D58">
+        <v>8.87261840531724</v>
+      </c>
+      <c r="E58">
+        <v>7.700000000000003</v>
+      </c>
+      <c r="F58">
+        <v>21</v>
+      </c>
+      <c r="G58">
+        <v>12.5</v>
+      </c>
+      <c r="H58">
+        <v>24.2</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1.94</v>
+      </c>
+      <c r="K58">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L58">
+        <v>1.96</v>
+      </c>
+      <c r="M58">
+        <v>5.014800000000001</v>
+      </c>
+      <c r="N58">
+        <v>-3.054800000000001</v>
+      </c>
+      <c r="O58">
+        <v>-0.4582200000000002</v>
+      </c>
+      <c r="P58">
+        <v>-2.596580000000001</v>
+      </c>
+      <c r="Q58">
+        <v>-2.616580000000001</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1602499365980596</v>
+      </c>
+      <c r="T58">
+        <v>1.646819187132722</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.05862646566164154</v>
+      </c>
+      <c r="W58">
+        <v>0.2248</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.3908431044109435</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1983979721031462</v>
+      </c>
+      <c r="C59">
+        <v>-0.1135687017417801</v>
+      </c>
+      <c r="D59">
+        <v>8.761431298258222</v>
+      </c>
+      <c r="E59">
+        <v>8.075000000000003</v>
+      </c>
+      <c r="F59">
+        <v>21.375</v>
+      </c>
+      <c r="G59">
+        <v>12.5</v>
+      </c>
+      <c r="H59">
+        <v>24.2</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1.94</v>
+      </c>
+      <c r="K59">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L59">
+        <v>1.96</v>
+      </c>
+      <c r="M59">
+        <v>5.104350000000001</v>
+      </c>
+      <c r="N59">
+        <v>-3.144350000000001</v>
+      </c>
+      <c r="O59">
+        <v>-0.4716525000000003</v>
+      </c>
+      <c r="P59">
+        <v>-2.672697500000001</v>
+      </c>
+      <c r="Q59">
+        <v>-2.692697500000001</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.163074353728247</v>
+      </c>
+      <c r="T59">
+        <v>1.685117307763715</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.05759793117634958</v>
+      </c>
+      <c r="W59">
+        <v>0.2250456140350877</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.3839862078423305</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2003979721031462</v>
+      </c>
+      <c r="C60">
+        <v>-0.597003618148598</v>
+      </c>
+      <c r="D60">
+        <v>8.6529963818514</v>
+      </c>
+      <c r="E60">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="F60">
+        <v>21.75</v>
+      </c>
+      <c r="G60">
+        <v>12.5</v>
+      </c>
+      <c r="H60">
+        <v>24.2</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>1.94</v>
+      </c>
+      <c r="K60">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L60">
+        <v>1.96</v>
+      </c>
+      <c r="M60">
+        <v>5.1939</v>
+      </c>
+      <c r="N60">
+        <v>-3.2339</v>
+      </c>
+      <c r="O60">
+        <v>-0.4850850000000001</v>
+      </c>
+      <c r="P60">
+        <v>-2.748815</v>
+      </c>
+      <c r="Q60">
+        <v>-2.768815</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1660332669122529</v>
+      </c>
+      <c r="T60">
+        <v>1.725239148424756</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.05660486339744701</v>
+      </c>
+      <c r="W60">
+        <v>0.2252827586206897</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.3773657559829801</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2023979721031463</v>
+      </c>
+      <c r="C61">
+        <v>-1.077787281241882</v>
+      </c>
+      <c r="D61">
+        <v>8.547212718758118</v>
+      </c>
+      <c r="E61">
+        <v>8.824999999999999</v>
+      </c>
+      <c r="F61">
+        <v>22.125</v>
+      </c>
+      <c r="G61">
+        <v>12.5</v>
+      </c>
+      <c r="H61">
+        <v>24.2</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1.94</v>
+      </c>
+      <c r="K61">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L61">
+        <v>1.96</v>
+      </c>
+      <c r="M61">
+        <v>5.28345</v>
+      </c>
+      <c r="N61">
+        <v>-3.32345</v>
+      </c>
+      <c r="O61">
+        <v>-0.4985175000000001</v>
+      </c>
+      <c r="P61">
+        <v>-2.8249325</v>
+      </c>
+      <c r="Q61">
+        <v>-2.8449325</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1691365173247469</v>
+      </c>
+      <c r="T61">
+        <v>1.767318152044872</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.0556454589330835</v>
+      </c>
+      <c r="W61">
+        <v>0.2255118644067797</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.3709697262205566</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2043979721031462</v>
+      </c>
+      <c r="C62">
+        <v>-1.55601575210062</v>
+      </c>
+      <c r="D62">
+        <v>8.44398424789938</v>
+      </c>
+      <c r="E62">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="F62">
+        <v>22.5</v>
+      </c>
+      <c r="G62">
+        <v>12.5</v>
+      </c>
+      <c r="H62">
+        <v>24.2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1.94</v>
+      </c>
+      <c r="K62">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L62">
+        <v>1.96</v>
+      </c>
+      <c r="M62">
+        <v>5.373</v>
+      </c>
+      <c r="N62">
+        <v>-3.413</v>
+      </c>
+      <c r="O62">
+        <v>-0.5119500000000001</v>
+      </c>
+      <c r="P62">
+        <v>-2.90105</v>
+      </c>
+      <c r="Q62">
+        <v>-2.92105</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1723949302578655</v>
+      </c>
+      <c r="T62">
+        <v>1.811501105845994</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.05471803461753211</v>
+      </c>
+      <c r="W62">
+        <v>0.2257333333333333</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.364786897450214</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2063979721031462</v>
+      </c>
+      <c r="C63">
+        <v>-2.03178050649398</v>
+      </c>
+      <c r="D63">
+        <v>8.343219493506018</v>
+      </c>
+      <c r="E63">
+        <v>9.574999999999999</v>
+      </c>
+      <c r="F63">
+        <v>22.875</v>
+      </c>
+      <c r="G63">
+        <v>12.5</v>
+      </c>
+      <c r="H63">
+        <v>24.2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1.94</v>
+      </c>
+      <c r="K63">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L63">
+        <v>1.96</v>
+      </c>
+      <c r="M63">
+        <v>5.46255</v>
+      </c>
+      <c r="N63">
+        <v>-3.50255</v>
+      </c>
+      <c r="O63">
+        <v>-0.5253825000000001</v>
+      </c>
+      <c r="P63">
+        <v>-2.9771675</v>
+      </c>
+      <c r="Q63">
+        <v>-2.9971675</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1758204412901185</v>
+      </c>
+      <c r="T63">
+        <v>1.857949852149737</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.05382101765658896</v>
+      </c>
+      <c r="W63">
+        <v>0.2259475409836066</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.3588067843772597</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2083979721031462</v>
+      </c>
+      <c r="C64">
+        <v>-2.505168705244753</v>
+      </c>
+      <c r="D64">
+        <v>8.244831294755247</v>
+      </c>
+      <c r="E64">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="F64">
+        <v>23.25</v>
+      </c>
+      <c r="G64">
+        <v>12.5</v>
+      </c>
+      <c r="H64">
+        <v>24.2</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1.94</v>
+      </c>
+      <c r="K64">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L64">
+        <v>1.96</v>
+      </c>
+      <c r="M64">
+        <v>5.5521</v>
+      </c>
+      <c r="N64">
+        <v>-3.5921</v>
+      </c>
+      <c r="O64">
+        <v>-0.5388150000000002</v>
+      </c>
+      <c r="P64">
+        <v>-3.053285</v>
+      </c>
+      <c r="Q64">
+        <v>-3.073285</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1794262423767006</v>
+      </c>
+      <c r="T64">
+        <v>1.906843269311572</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.05295293672664398</v>
+      </c>
+      <c r="W64">
+        <v>0.2261548387096774</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.3530195781776264</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2103979721031462</v>
+      </c>
+      <c r="C65">
+        <v>-2.976263445686079</v>
+      </c>
+      <c r="D65">
+        <v>8.148736554313921</v>
+      </c>
+      <c r="E65">
+        <v>10.325</v>
+      </c>
+      <c r="F65">
+        <v>23.625</v>
+      </c>
+      <c r="G65">
+        <v>12.5</v>
+      </c>
+      <c r="H65">
+        <v>24.2</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>1.94</v>
+      </c>
+      <c r="K65">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L65">
+        <v>1.96</v>
+      </c>
+      <c r="M65">
+        <v>5.64165</v>
+      </c>
+      <c r="N65">
+        <v>-3.68165</v>
+      </c>
+      <c r="O65">
+        <v>-0.5522475000000001</v>
+      </c>
+      <c r="P65">
+        <v>-3.1294025</v>
+      </c>
+      <c r="Q65">
+        <v>-3.1494025</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1832269516301249</v>
+      </c>
+      <c r="T65">
+        <v>1.95837957388756</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.05211241392145916</v>
+      </c>
+      <c r="W65">
+        <v>0.2263555555555556</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.3474160928097276</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2123979721031462</v>
+      </c>
+      <c r="C66">
+        <v>-3.445143995736196</v>
+      </c>
+      <c r="D66">
+        <v>8.054856004263803</v>
+      </c>
+      <c r="E66">
+        <v>10.7</v>
+      </c>
+      <c r="F66">
+        <v>24</v>
+      </c>
+      <c r="G66">
+        <v>12.5</v>
+      </c>
+      <c r="H66">
+        <v>24.2</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1.94</v>
+      </c>
+      <c r="K66">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L66">
+        <v>1.96</v>
+      </c>
+      <c r="M66">
+        <v>5.7312</v>
+      </c>
+      <c r="N66">
+        <v>-3.7712</v>
+      </c>
+      <c r="O66">
+        <v>-0.5656800000000002</v>
+      </c>
+      <c r="P66">
+        <v>-3.20552</v>
+      </c>
+      <c r="Q66">
+        <v>-3.22552</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1872388113976284</v>
+      </c>
+      <c r="T66">
+        <v>2.012779006495549</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.05129815745393635</v>
+      </c>
+      <c r="W66">
+        <v>0.22655</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.3419877163595756</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2143979721031462</v>
+      </c>
+      <c r="C67">
+        <v>-3.911886011976932</v>
+      </c>
+      <c r="D67">
+        <v>7.963113988023066</v>
+      </c>
+      <c r="E67">
+        <v>11.075</v>
+      </c>
+      <c r="F67">
+        <v>24.375</v>
+      </c>
+      <c r="G67">
+        <v>12.5</v>
+      </c>
+      <c r="H67">
+        <v>24.2</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1.94</v>
+      </c>
+      <c r="K67">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L67">
+        <v>1.96</v>
+      </c>
+      <c r="M67">
+        <v>5.82075</v>
+      </c>
+      <c r="N67">
+        <v>-3.86075</v>
+      </c>
+      <c r="O67">
+        <v>-0.5791125000000001</v>
+      </c>
+      <c r="P67">
+        <v>-3.2816375</v>
+      </c>
+      <c r="Q67">
+        <v>-3.3016375</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1914799202947035</v>
+      </c>
+      <c r="T67">
+        <v>2.070286978109707</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.0505089550315681</v>
+      </c>
+      <c r="W67">
+        <v>0.2267384615384616</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.3367263668771207</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2163979721031462</v>
+      </c>
+      <c r="C68">
+        <v>-4.376561742997087</v>
+      </c>
+      <c r="D68">
+        <v>7.873438257002912</v>
+      </c>
+      <c r="E68">
+        <v>11.45</v>
+      </c>
+      <c r="F68">
+        <v>24.75</v>
+      </c>
+      <c r="G68">
+        <v>12.5</v>
+      </c>
+      <c r="H68">
+        <v>24.2</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>1.94</v>
+      </c>
+      <c r="K68">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L68">
+        <v>1.96</v>
+      </c>
+      <c r="M68">
+        <v>5.9103</v>
+      </c>
+      <c r="N68">
+        <v>-3.9503</v>
+      </c>
+      <c r="O68">
+        <v>-0.5925450000000001</v>
+      </c>
+      <c r="P68">
+        <v>-3.357755</v>
+      </c>
+      <c r="Q68">
+        <v>-3.377755</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.1959705061857242</v>
+      </c>
+      <c r="T68">
+        <v>2.131177771583522</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0497436678341201</v>
+      </c>
+      <c r="W68">
+        <v>0.2269212121212121</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.3316244522274673</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2183979721031462</v>
+      </c>
+      <c r="C69">
+        <v>-4.839240219149158</v>
+      </c>
+      <c r="D69">
+        <v>7.785759780850842</v>
+      </c>
+      <c r="E69">
+        <v>11.825</v>
+      </c>
+      <c r="F69">
+        <v>25.125</v>
+      </c>
+      <c r="G69">
+        <v>12.5</v>
+      </c>
+      <c r="H69">
+        <v>24.2</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>1.94</v>
+      </c>
+      <c r="K69">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L69">
+        <v>1.96</v>
+      </c>
+      <c r="M69">
+        <v>5.99985</v>
+      </c>
+      <c r="N69">
+        <v>-4.03985</v>
+      </c>
+      <c r="O69">
+        <v>-0.6059775000000002</v>
+      </c>
+      <c r="P69">
+        <v>-3.4338725</v>
+      </c>
+      <c r="Q69">
+        <v>-3.4538725</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2007332487974128</v>
+      </c>
+      <c r="T69">
+        <v>2.195758916176962</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.04900122503062577</v>
+      </c>
+      <c r="W69">
+        <v>0.2270985074626866</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.326674833537505</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2203979721031462</v>
+      </c>
+      <c r="C70">
+        <v>-5.299987429767004</v>
+      </c>
+      <c r="D70">
+        <v>7.700012570232998</v>
+      </c>
+      <c r="E70">
+        <v>12.2</v>
+      </c>
+      <c r="F70">
+        <v>25.5</v>
+      </c>
+      <c r="G70">
+        <v>12.5</v>
+      </c>
+      <c r="H70">
+        <v>24.2</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>1.94</v>
+      </c>
+      <c r="K70">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L70">
+        <v>1.96</v>
+      </c>
+      <c r="M70">
+        <v>6.089400000000001</v>
+      </c>
+      <c r="N70">
+        <v>-4.129400000000001</v>
+      </c>
+      <c r="O70">
+        <v>-0.6194100000000002</v>
+      </c>
+      <c r="P70">
+        <v>-3.509990000000001</v>
+      </c>
+      <c r="Q70">
+        <v>-3.529990000000001</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.205793662822332</v>
+      </c>
+      <c r="T70">
+        <v>2.264376382307492</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.04828061878017539</v>
+      </c>
+      <c r="W70">
+        <v>0.2272705882352941</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3218707918678358</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2223979721031462</v>
+      </c>
+      <c r="C71">
+        <v>-5.758866488800479</v>
+      </c>
+      <c r="D71">
+        <v>7.616133511199524</v>
+      </c>
+      <c r="E71">
+        <v>12.575</v>
+      </c>
+      <c r="F71">
+        <v>25.875</v>
+      </c>
+      <c r="G71">
+        <v>12.5</v>
+      </c>
+      <c r="H71">
+        <v>24.2</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>1.94</v>
+      </c>
+      <c r="K71">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L71">
+        <v>1.96</v>
+      </c>
+      <c r="M71">
+        <v>6.178950000000001</v>
+      </c>
+      <c r="N71">
+        <v>-4.218950000000001</v>
+      </c>
+      <c r="O71">
+        <v>-0.6328425000000003</v>
+      </c>
+      <c r="P71">
+        <v>-3.586107500000001</v>
+      </c>
+      <c r="Q71">
+        <v>-3.606107500000001</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2111805551714395</v>
+      </c>
+      <c r="T71">
+        <v>2.337420781736767</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.04758089966741922</v>
+      </c>
+      <c r="W71">
+        <v>0.2274376811594203</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3172059977827948</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2243979721031462</v>
+      </c>
+      <c r="C72">
+        <v>-6.215937789740842</v>
+      </c>
+      <c r="D72">
+        <v>7.534062210259163</v>
+      </c>
+      <c r="E72">
+        <v>12.95</v>
+      </c>
+      <c r="F72">
+        <v>26.25</v>
+      </c>
+      <c r="G72">
+        <v>12.5</v>
+      </c>
+      <c r="H72">
+        <v>24.2</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>1.94</v>
+      </c>
+      <c r="K72">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L72">
+        <v>1.96</v>
+      </c>
+      <c r="M72">
+        <v>6.268500000000001</v>
+      </c>
+      <c r="N72">
+        <v>-4.308500000000001</v>
+      </c>
+      <c r="O72">
+        <v>-0.6462750000000003</v>
+      </c>
+      <c r="P72">
+        <v>-3.662225000000001</v>
+      </c>
+      <c r="Q72">
+        <v>-3.682225000000001</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2169265736771541</v>
+      </c>
+      <c r="T72">
+        <v>2.415334807794658</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.04690117252931323</v>
+      </c>
+      <c r="W72">
+        <v>0.2276</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3126744835287548</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2263979721031463</v>
+      </c>
+      <c r="C73">
+        <v>-6.671259150636114</v>
+      </c>
+      <c r="D73">
+        <v>7.453740849363885</v>
+      </c>
+      <c r="E73">
+        <v>13.325</v>
+      </c>
+      <c r="F73">
+        <v>26.625</v>
+      </c>
+      <c r="G73">
+        <v>12.5</v>
+      </c>
+      <c r="H73">
+        <v>24.2</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1.94</v>
+      </c>
+      <c r="K73">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L73">
+        <v>1.96</v>
+      </c>
+      <c r="M73">
+        <v>6.35805</v>
+      </c>
+      <c r="N73">
+        <v>-4.39805</v>
+      </c>
+      <c r="O73">
+        <v>-0.6597075000000001</v>
+      </c>
+      <c r="P73">
+        <v>-3.7383425</v>
+      </c>
+      <c r="Q73">
+        <v>-3.7583425</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2230688693211939</v>
+      </c>
+      <c r="T73">
+        <v>2.498622214959991</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.04624059263453417</v>
+      </c>
+      <c r="W73">
+        <v>0.2277577464788733</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3082706175635611</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2283979721031462</v>
+      </c>
+      <c r="C74">
+        <v>-7.124885949928132</v>
+      </c>
+      <c r="D74">
+        <v>7.375114050071868</v>
+      </c>
+      <c r="E74">
+        <v>13.7</v>
+      </c>
+      <c r="F74">
+        <v>27</v>
+      </c>
+      <c r="G74">
+        <v>12.5</v>
+      </c>
+      <c r="H74">
+        <v>24.2</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>1.94</v>
+      </c>
+      <c r="K74">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L74">
+        <v>1.96</v>
+      </c>
+      <c r="M74">
+        <v>6.4476</v>
+      </c>
+      <c r="N74">
+        <v>-4.4876</v>
+      </c>
+      <c r="O74">
+        <v>-0.6731400000000002</v>
+      </c>
+      <c r="P74">
+        <v>-3.81446</v>
+      </c>
+      <c r="Q74">
+        <v>-3.83446</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2296499003683793</v>
+      </c>
+      <c r="T74">
+        <v>2.587858722637133</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.04559836218127675</v>
+      </c>
+      <c r="W74">
+        <v>0.2279111111111111</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3039890812085116</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2303979721031462</v>
+      </c>
+      <c r="C75">
+        <v>-7.576871253781988</v>
+      </c>
+      <c r="D75">
+        <v>7.29812874621801</v>
+      </c>
+      <c r="E75">
+        <v>14.075</v>
+      </c>
+      <c r="F75">
+        <v>27.375</v>
+      </c>
+      <c r="G75">
+        <v>12.5</v>
+      </c>
+      <c r="H75">
+        <v>24.2</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>1.94</v>
+      </c>
+      <c r="K75">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L75">
+        <v>1.96</v>
+      </c>
+      <c r="M75">
+        <v>6.53715</v>
+      </c>
+      <c r="N75">
+        <v>-4.57715</v>
+      </c>
+      <c r="O75">
+        <v>-0.6865725000000001</v>
+      </c>
+      <c r="P75">
+        <v>-3.8905775</v>
+      </c>
+      <c r="Q75">
+        <v>-3.9105775</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2367184151968378</v>
+      </c>
+      <c r="T75">
+        <v>2.683705341994064</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.04497372708290311</v>
+      </c>
+      <c r="W75">
+        <v>0.2280602739726027</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.299824847219354</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2323979721031462</v>
+      </c>
+      <c r="C76">
+        <v>-8.027265935523072</v>
+      </c>
+      <c r="D76">
+        <v>7.222734064476927</v>
+      </c>
+      <c r="E76">
+        <v>14.45</v>
+      </c>
+      <c r="F76">
+        <v>27.75</v>
+      </c>
+      <c r="G76">
+        <v>12.5</v>
+      </c>
+      <c r="H76">
+        <v>24.2</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>1.94</v>
+      </c>
+      <c r="K76">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L76">
+        <v>1.96</v>
+      </c>
+      <c r="M76">
+        <v>6.6267</v>
+      </c>
+      <c r="N76">
+        <v>-4.666700000000001</v>
+      </c>
+      <c r="O76">
+        <v>-0.7000050000000002</v>
+      </c>
+      <c r="P76">
+        <v>-3.966695000000001</v>
+      </c>
+      <c r="Q76">
+        <v>-3.986695000000001</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2443306619351777</v>
+      </c>
+      <c r="T76">
+        <v>2.786924778224605</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.04436597401421522</v>
+      </c>
+      <c r="W76">
+        <v>0.2282054054054054</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.2957731600947681</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2343979721031462</v>
+      </c>
+      <c r="C77">
+        <v>-8.476118787746593</v>
+      </c>
+      <c r="D77">
+        <v>7.148881212253408</v>
+      </c>
+      <c r="E77">
+        <v>14.825</v>
+      </c>
+      <c r="F77">
+        <v>28.125</v>
+      </c>
+      <c r="G77">
+        <v>12.5</v>
+      </c>
+      <c r="H77">
+        <v>24.2</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>1.94</v>
+      </c>
+      <c r="K77">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L77">
+        <v>1.96</v>
+      </c>
+      <c r="M77">
+        <v>6.71625</v>
+      </c>
+      <c r="N77">
+        <v>-4.756250000000001</v>
+      </c>
+      <c r="O77">
+        <v>-0.7134375000000002</v>
+      </c>
+      <c r="P77">
+        <v>-4.0428125</v>
+      </c>
+      <c r="Q77">
+        <v>-4.0628125</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2525518884125849</v>
+      </c>
+      <c r="T77">
+        <v>2.89840176935359</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.04377442769402569</v>
+      </c>
+      <c r="W77">
+        <v>0.2283466666666667</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.2918295179601712</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2363979721031463</v>
+      </c>
+      <c r="C78">
+        <v>-8.923476627618779</v>
+      </c>
+      <c r="D78">
+        <v>7.076523372381222</v>
+      </c>
+      <c r="E78">
+        <v>15.2</v>
+      </c>
+      <c r="F78">
+        <v>28.5</v>
+      </c>
+      <c r="G78">
+        <v>12.5</v>
+      </c>
+      <c r="H78">
+        <v>24.2</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>1.94</v>
+      </c>
+      <c r="K78">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L78">
+        <v>1.96</v>
+      </c>
+      <c r="M78">
+        <v>6.805800000000001</v>
+      </c>
+      <c r="N78">
+        <v>-4.845800000000001</v>
+      </c>
+      <c r="O78">
+        <v>-0.7268700000000002</v>
+      </c>
+      <c r="P78">
+        <v>-4.118930000000001</v>
+      </c>
+      <c r="Q78">
+        <v>-4.13893</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2614582170964426</v>
+      </c>
+      <c r="T78">
+        <v>3.019168509743323</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.04319844838226219</v>
+      </c>
+      <c r="W78">
+        <v>0.2284842105263158</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.2879896558817479</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2383979721031463</v>
+      </c>
+      <c r="C79">
+        <v>-9.369384395847245</v>
+      </c>
+      <c r="D79">
+        <v>7.005615604152754</v>
+      </c>
+      <c r="E79">
+        <v>15.575</v>
+      </c>
+      <c r="F79">
+        <v>28.875</v>
+      </c>
+      <c r="G79">
+        <v>12.5</v>
+      </c>
+      <c r="H79">
+        <v>24.2</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>1.94</v>
+      </c>
+      <c r="K79">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L79">
+        <v>1.96</v>
+      </c>
+      <c r="M79">
+        <v>6.895350000000001</v>
+      </c>
+      <c r="N79">
+        <v>-4.935350000000001</v>
+      </c>
+      <c r="O79">
+        <v>-0.7403025000000002</v>
+      </c>
+      <c r="P79">
+        <v>-4.1950475</v>
+      </c>
+      <c r="Q79">
+        <v>-4.215047500000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.271139009144114</v>
+      </c>
+      <c r="T79">
+        <v>3.15043670581912</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.04263742957210295</v>
+      </c>
+      <c r="W79">
+        <v>0.2286181818181818</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.2842495304806862</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2403979721031463</v>
+      </c>
+      <c r="C80">
+        <v>-9.813885249760286</v>
+      </c>
+      <c r="D80">
+        <v>6.936114750239714</v>
+      </c>
+      <c r="E80">
+        <v>15.95</v>
+      </c>
+      <c r="F80">
+        <v>29.25</v>
+      </c>
+      <c r="G80">
+        <v>12.5</v>
+      </c>
+      <c r="H80">
+        <v>24.2</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1.94</v>
+      </c>
+      <c r="K80">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L80">
+        <v>1.96</v>
+      </c>
+      <c r="M80">
+        <v>6.984900000000001</v>
+      </c>
+      <c r="N80">
+        <v>-5.024900000000001</v>
+      </c>
+      <c r="O80">
+        <v>-0.7537350000000002</v>
+      </c>
+      <c r="P80">
+        <v>-4.271165000000001</v>
+      </c>
+      <c r="Q80">
+        <v>-4.291165000000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.2816998731961192</v>
+      </c>
+      <c r="T80">
+        <v>3.293638374265443</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.04209079585964008</v>
+      </c>
+      <c r="W80">
+        <v>0.228748717948718</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.2806053057309339</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2423979721031462</v>
+      </c>
+      <c r="C81">
+        <v>-10.2570206509</v>
+      </c>
+      <c r="D81">
+        <v>6.867979349100006</v>
+      </c>
+      <c r="E81">
+        <v>16.325</v>
+      </c>
+      <c r="F81">
+        <v>29.625</v>
+      </c>
+      <c r="G81">
+        <v>12.5</v>
+      </c>
+      <c r="H81">
+        <v>24.2</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>1.94</v>
+      </c>
+      <c r="K81">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L81">
+        <v>1.96</v>
+      </c>
+      <c r="M81">
+        <v>7.074450000000001</v>
+      </c>
+      <c r="N81">
+        <v>-5.114450000000001</v>
+      </c>
+      <c r="O81">
+        <v>-0.7671675000000002</v>
+      </c>
+      <c r="P81">
+        <v>-4.3472825</v>
+      </c>
+      <c r="Q81">
+        <v>-4.3672825</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.2932665338245058</v>
+      </c>
+      <c r="T81">
+        <v>3.450478296849512</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.04155800097534085</v>
+      </c>
+      <c r="W81">
+        <v>0.2288759493670886</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.2770533398356055</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2443979721031462</v>
+      </c>
+      <c r="C82">
+        <v>-10.69883044750299</v>
+      </c>
+      <c r="D82">
+        <v>6.801169552497011</v>
+      </c>
+      <c r="E82">
+        <v>16.7</v>
+      </c>
+      <c r="F82">
+        <v>30</v>
+      </c>
+      <c r="G82">
+        <v>12.5</v>
+      </c>
+      <c r="H82">
+        <v>24.2</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>1.94</v>
+      </c>
+      <c r="K82">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L82">
+        <v>1.96</v>
+      </c>
+      <c r="M82">
+        <v>7.164000000000001</v>
+      </c>
+      <c r="N82">
+        <v>-5.204000000000001</v>
+      </c>
+      <c r="O82">
+        <v>-0.7806000000000002</v>
+      </c>
+      <c r="P82">
+        <v>-4.423400000000001</v>
+      </c>
+      <c r="Q82">
+        <v>-4.4434</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3059898605157311</v>
+      </c>
+      <c r="T82">
+        <v>3.623002211691988</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.04103852596314908</v>
+      </c>
+      <c r="W82">
+        <v>0.229</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.2735901730876605</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2463979721031463</v>
+      </c>
+      <c r="C83">
+        <v>-11.13935295221338</v>
+      </c>
+      <c r="D83">
+        <v>6.735647047786625</v>
+      </c>
+      <c r="E83">
+        <v>17.075</v>
+      </c>
+      <c r="F83">
+        <v>30.375</v>
+      </c>
+      <c r="G83">
+        <v>12.5</v>
+      </c>
+      <c r="H83">
+        <v>24.2</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>1.94</v>
+      </c>
+      <c r="K83">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L83">
+        <v>1.96</v>
+      </c>
+      <c r="M83">
+        <v>7.253550000000001</v>
+      </c>
+      <c r="N83">
+        <v>-5.293550000000002</v>
+      </c>
+      <c r="O83">
+        <v>-0.7940325000000004</v>
+      </c>
+      <c r="P83">
+        <v>-4.499517500000001</v>
+      </c>
+      <c r="Q83">
+        <v>-4.519517500000001</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3200524847534013</v>
+      </c>
+      <c r="T83">
+        <v>3.813686538623146</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.04053187749446822</v>
+      </c>
+      <c r="W83">
+        <v>0.229120987654321</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.2702125166297881</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2483979721031462</v>
+      </c>
+      <c r="C84">
+        <v>-11.57862501534643</v>
+      </c>
+      <c r="D84">
+        <v>6.671374984653577</v>
+      </c>
+      <c r="E84">
+        <v>17.45</v>
+      </c>
+      <c r="F84">
+        <v>30.75</v>
+      </c>
+      <c r="G84">
+        <v>12.5</v>
+      </c>
+      <c r="H84">
+        <v>24.2</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>1.94</v>
+      </c>
+      <c r="K84">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L84">
+        <v>1.96</v>
+      </c>
+      <c r="M84">
+        <v>7.343100000000002</v>
+      </c>
+      <c r="N84">
+        <v>-5.383100000000002</v>
+      </c>
+      <c r="O84">
+        <v>-0.8074650000000003</v>
+      </c>
+      <c r="P84">
+        <v>-4.575635000000001</v>
+      </c>
+      <c r="Q84">
+        <v>-4.595635000000001</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3356776227952569</v>
+      </c>
+      <c r="T84">
+        <v>4.025558012991098</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0400375863055113</v>
+      </c>
+      <c r="W84">
+        <v>0.2292390243902439</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.2669172420367419</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2503979721031462</v>
+      </c>
+      <c r="C85">
+        <v>-12.01668209399746</v>
+      </c>
+      <c r="D85">
+        <v>6.608317906002545</v>
+      </c>
+      <c r="E85">
+        <v>17.825</v>
+      </c>
+      <c r="F85">
+        <v>31.125</v>
+      </c>
+      <c r="G85">
+        <v>12.5</v>
+      </c>
+      <c r="H85">
+        <v>24.2</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>1.94</v>
+      </c>
+      <c r="K85">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L85">
+        <v>1.96</v>
+      </c>
+      <c r="M85">
+        <v>7.432650000000002</v>
+      </c>
+      <c r="N85">
+        <v>-5.472650000000002</v>
+      </c>
+      <c r="O85">
+        <v>-0.8208975000000004</v>
+      </c>
+      <c r="P85">
+        <v>-4.651752500000002</v>
+      </c>
+      <c r="Q85">
+        <v>-4.671752500000002</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.3531410123714485</v>
+      </c>
+      <c r="T85">
+        <v>4.262355543167045</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03955520574761356</v>
+      </c>
+      <c r="W85">
+        <v>0.2293542168674699</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.263701371650757</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2523979721031462</v>
+      </c>
+      <c r="C86">
+        <v>-12.45355831726807</v>
+      </c>
+      <c r="D86">
+        <v>6.546441682731927</v>
+      </c>
+      <c r="E86">
+        <v>18.2</v>
+      </c>
+      <c r="F86">
+        <v>31.5</v>
+      </c>
+      <c r="G86">
+        <v>12.5</v>
+      </c>
+      <c r="H86">
+        <v>24.2</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>1.94</v>
+      </c>
+      <c r="K86">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L86">
+        <v>1.96</v>
+      </c>
+      <c r="M86">
+        <v>7.522200000000001</v>
+      </c>
+      <c r="N86">
+        <v>-5.562200000000001</v>
+      </c>
+      <c r="O86">
+        <v>-0.8343300000000002</v>
+      </c>
+      <c r="P86">
+        <v>-4.72787</v>
+      </c>
+      <c r="Q86">
+        <v>-4.747870000000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.3727873256446638</v>
+      </c>
+      <c r="T86">
+        <v>4.528752764614983</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03908431044109437</v>
+      </c>
+      <c r="W86">
+        <v>0.2294666666666667</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.2605620696072957</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2543979721031462</v>
+      </c>
+      <c r="C87">
+        <v>-12.88928654786201</v>
+      </c>
+      <c r="D87">
+        <v>6.485713452137995</v>
+      </c>
+      <c r="E87">
+        <v>18.575</v>
+      </c>
+      <c r="F87">
+        <v>31.875</v>
+      </c>
+      <c r="G87">
+        <v>12.5</v>
+      </c>
+      <c r="H87">
+        <v>24.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1.94</v>
+      </c>
+      <c r="K87">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L87">
+        <v>1.96</v>
+      </c>
+      <c r="M87">
+        <v>7.611750000000001</v>
+      </c>
+      <c r="N87">
+        <v>-5.651750000000001</v>
+      </c>
+      <c r="O87">
+        <v>-0.8477625000000002</v>
+      </c>
+      <c r="P87">
+        <v>-4.803987500000001</v>
+      </c>
+      <c r="Q87">
+        <v>-4.823987500000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.3950531473543081</v>
+      </c>
+      <c r="T87">
+        <v>4.830669615589316</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03862449502414031</v>
+      </c>
+      <c r="W87">
+        <v>0.2295764705882353</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.2574966334942687</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2563979721031462</v>
+      </c>
+      <c r="C88">
+        <v>-13.32389844028409</v>
+      </c>
+      <c r="D88">
+        <v>6.426101559715914</v>
+      </c>
+      <c r="E88">
+        <v>18.95</v>
+      </c>
+      <c r="F88">
+        <v>32.25</v>
+      </c>
+      <c r="G88">
+        <v>12.5</v>
+      </c>
+      <c r="H88">
+        <v>24.2</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1.94</v>
+      </c>
+      <c r="K88">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L88">
+        <v>1.96</v>
+      </c>
+      <c r="M88">
+        <v>7.701300000000001</v>
+      </c>
+      <c r="N88">
+        <v>-5.741300000000001</v>
+      </c>
+      <c r="O88">
+        <v>-0.8611950000000003</v>
+      </c>
+      <c r="P88">
+        <v>-4.880105</v>
+      </c>
+      <c r="Q88">
+        <v>-4.900105</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4204998007367587</v>
+      </c>
+      <c r="T88">
+        <v>5.175717445274267</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03817537298897589</v>
+      </c>
+      <c r="W88">
+        <v>0.2296837209302326</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.2545024865931725</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2583979721031462</v>
+      </c>
+      <c r="C89">
+        <v>-13.75742449585893</v>
+      </c>
+      <c r="D89">
+        <v>6.367575504141071</v>
+      </c>
+      <c r="E89">
+        <v>19.325</v>
+      </c>
+      <c r="F89">
+        <v>32.625</v>
+      </c>
+      <c r="G89">
+        <v>12.5</v>
+      </c>
+      <c r="H89">
+        <v>24.2</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1.94</v>
+      </c>
+      <c r="K89">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L89">
+        <v>1.96</v>
+      </c>
+      <c r="M89">
+        <v>7.790850000000001</v>
+      </c>
+      <c r="N89">
+        <v>-5.830850000000001</v>
+      </c>
+      <c r="O89">
+        <v>-0.8746275000000002</v>
+      </c>
+      <c r="P89">
+        <v>-4.956222500000001</v>
+      </c>
+      <c r="Q89">
+        <v>-4.9762225</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.4498613238703555</v>
+      </c>
+      <c r="T89">
+        <v>5.57384955644921</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.037736575598298</v>
+      </c>
+      <c r="W89">
+        <v>0.2297885057471264</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.25157717065532</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2603979721031462</v>
+      </c>
+      <c r="C90">
+        <v>-14.18989411477022</v>
+      </c>
+      <c r="D90">
+        <v>6.31010588522978</v>
+      </c>
+      <c r="E90">
+        <v>19.7</v>
+      </c>
+      <c r="F90">
+        <v>33</v>
+      </c>
+      <c r="G90">
+        <v>12.5</v>
+      </c>
+      <c r="H90">
+        <v>24.2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1.94</v>
+      </c>
+      <c r="K90">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L90">
+        <v>1.96</v>
+      </c>
+      <c r="M90">
+        <v>7.880400000000001</v>
+      </c>
+      <c r="N90">
+        <v>-5.920400000000001</v>
+      </c>
+      <c r="O90">
+        <v>-0.8880600000000003</v>
+      </c>
+      <c r="P90">
+        <v>-5.03234</v>
+      </c>
+      <c r="Q90">
+        <v>-5.052340000000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.4841164341928852</v>
+      </c>
+      <c r="T90">
+        <v>6.038337019486646</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.03730775087559007</v>
+      </c>
+      <c r="W90">
+        <v>0.2298909090909091</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.2487183391706005</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2623979721031462</v>
+      </c>
+      <c r="C91">
+        <v>-14.62133564530717</v>
+      </c>
+      <c r="D91">
+        <v>6.253664354692831</v>
+      </c>
+      <c r="E91">
+        <v>20.075</v>
+      </c>
+      <c r="F91">
+        <v>33.375</v>
+      </c>
+      <c r="G91">
+        <v>12.5</v>
+      </c>
+      <c r="H91">
+        <v>24.2</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1.94</v>
+      </c>
+      <c r="K91">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L91">
+        <v>1.96</v>
+      </c>
+      <c r="M91">
+        <v>7.969950000000001</v>
+      </c>
+      <c r="N91">
+        <v>-6.009950000000001</v>
+      </c>
+      <c r="O91">
+        <v>-0.9014925000000003</v>
+      </c>
+      <c r="P91">
+        <v>-5.1084575</v>
+      </c>
+      <c r="Q91">
+        <v>-5.1284575</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5245997463922384</v>
+      </c>
+      <c r="T91">
+        <v>6.587276748530886</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.03688856266350479</v>
+      </c>
+      <c r="W91">
+        <v>0.2299910112359551</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.245923751090032</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2643979721031462</v>
+      </c>
+      <c r="C92">
+        <v>-15.05177643049147</v>
+      </c>
+      <c r="D92">
+        <v>6.198223569508526</v>
+      </c>
+      <c r="E92">
+        <v>20.45</v>
+      </c>
+      <c r="F92">
+        <v>33.75</v>
+      </c>
+      <c r="G92">
+        <v>12.5</v>
+      </c>
+      <c r="H92">
+        <v>24.2</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1.94</v>
+      </c>
+      <c r="K92">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L92">
+        <v>1.96</v>
+      </c>
+      <c r="M92">
+        <v>8.0595</v>
+      </c>
+      <c r="N92">
+        <v>-6.0995</v>
+      </c>
+      <c r="O92">
+        <v>-0.9149250000000001</v>
+      </c>
+      <c r="P92">
+        <v>-5.184575</v>
+      </c>
+      <c r="Q92">
+        <v>-5.204575</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.5731797210314622</v>
+      </c>
+      <c r="T92">
+        <v>7.246004423383975</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.03647868974502141</v>
+      </c>
+      <c r="W92">
+        <v>0.2300888888888889</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2431912649668093</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2663979721031462</v>
+      </c>
+      <c r="C93">
+        <v>-15.48124285224588</v>
+      </c>
+      <c r="D93">
+        <v>6.143757147754123</v>
+      </c>
+      <c r="E93">
+        <v>20.825</v>
+      </c>
+      <c r="F93">
+        <v>34.125</v>
+      </c>
+      <c r="G93">
+        <v>12.5</v>
+      </c>
+      <c r="H93">
+        <v>24.2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>1.94</v>
+      </c>
+      <c r="K93">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L93">
+        <v>1.96</v>
+      </c>
+      <c r="M93">
+        <v>8.149050000000001</v>
+      </c>
+      <c r="N93">
+        <v>-6.189050000000001</v>
+      </c>
+      <c r="O93">
+        <v>-0.9283575000000003</v>
+      </c>
+      <c r="P93">
+        <v>-5.2606925</v>
+      </c>
+      <c r="Q93">
+        <v>-5.280692500000001</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6325552455905137</v>
+      </c>
+      <c r="T93">
+        <v>8.051116025982196</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.03607782502254864</v>
+      </c>
+      <c r="W93">
+        <v>0.2301846153846154</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2405188334836575</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2683979721031463</v>
+      </c>
+      <c r="C94">
+        <v>-15.90976037325424</v>
+      </c>
+      <c r="D94">
+        <v>6.090239626745755</v>
+      </c>
+      <c r="E94">
+        <v>21.2</v>
+      </c>
+      <c r="F94">
+        <v>34.5</v>
+      </c>
+      <c r="G94">
+        <v>12.5</v>
+      </c>
+      <c r="H94">
+        <v>24.2</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1.94</v>
+      </c>
+      <c r="K94">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L94">
+        <v>1.96</v>
+      </c>
+      <c r="M94">
+        <v>8.2386</v>
+      </c>
+      <c r="N94">
+        <v>-6.2786</v>
+      </c>
+      <c r="O94">
+        <v>-0.9417900000000001</v>
+      </c>
+      <c r="P94">
+        <v>-5.33681</v>
+      </c>
+      <c r="Q94">
+        <v>-5.356809999999999</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.706774651289328</v>
+      </c>
+      <c r="T94">
+        <v>9.057505529229973</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.03568567475056442</v>
+      </c>
+      <c r="W94">
+        <v>0.2302782608695652</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2379044983370961</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2703979721031463</v>
+      </c>
+      <c r="C95">
+        <v>-16.3373535766527</v>
+      </c>
+      <c r="D95">
+        <v>6.037646423347296</v>
+      </c>
+      <c r="E95">
+        <v>21.575</v>
+      </c>
+      <c r="F95">
+        <v>34.875</v>
+      </c>
+      <c r="G95">
+        <v>12.5</v>
+      </c>
+      <c r="H95">
+        <v>24.2</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1.94</v>
+      </c>
+      <c r="K95">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L95">
+        <v>1.96</v>
+      </c>
+      <c r="M95">
+        <v>8.328150000000001</v>
+      </c>
+      <c r="N95">
+        <v>-6.368150000000001</v>
+      </c>
+      <c r="O95">
+        <v>-0.9552225000000003</v>
+      </c>
+      <c r="P95">
+        <v>-5.4129275</v>
+      </c>
+      <c r="Q95">
+        <v>-5.4329275</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.802199601473518</v>
+      </c>
+      <c r="T95">
+        <v>10.35143489054854</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.03530195781776265</v>
+      </c>
+      <c r="W95">
+        <v>0.2303698924731183</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.235346385451751</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2723979721031463</v>
+      </c>
+      <c r="C96">
+        <v>-16.76404620368186</v>
+      </c>
+      <c r="D96">
+        <v>5.985953796318144</v>
+      </c>
+      <c r="E96">
+        <v>21.95</v>
+      </c>
+      <c r="F96">
+        <v>35.25</v>
+      </c>
+      <c r="G96">
+        <v>12.5</v>
+      </c>
+      <c r="H96">
+        <v>24.2</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>1.94</v>
+      </c>
+      <c r="K96">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L96">
+        <v>1.96</v>
+      </c>
+      <c r="M96">
+        <v>8.4177</v>
+      </c>
+      <c r="N96">
+        <v>-6.4577</v>
+      </c>
+      <c r="O96">
+        <v>-0.9686550000000002</v>
+      </c>
+      <c r="P96">
+        <v>-5.489045</v>
+      </c>
+      <c r="Q96">
+        <v>-5.509045</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>0.9294328683857713</v>
+      </c>
+      <c r="T96">
+        <v>12.0766740389733</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.0349264050750205</v>
+      </c>
+      <c r="W96">
+        <v>0.2304595744680851</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2328427005001367</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2743979721031463</v>
+      </c>
+      <c r="C97">
+        <v>-17.18986118942119</v>
+      </c>
+      <c r="D97">
+        <v>5.935138810578813</v>
+      </c>
+      <c r="E97">
+        <v>22.325</v>
+      </c>
+      <c r="F97">
+        <v>35.625</v>
+      </c>
+      <c r="G97">
+        <v>12.5</v>
+      </c>
+      <c r="H97">
+        <v>24.2</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1.94</v>
+      </c>
+      <c r="K97">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L97">
+        <v>1.96</v>
+      </c>
+      <c r="M97">
+        <v>8.507250000000001</v>
+      </c>
+      <c r="N97">
+        <v>-6.547250000000001</v>
+      </c>
+      <c r="O97">
+        <v>-0.9820875000000003</v>
+      </c>
+      <c r="P97">
+        <v>-5.5651625</v>
+      </c>
+      <c r="Q97">
+        <v>-5.585162500000001</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.107559442062926</v>
+      </c>
+      <c r="T97">
+        <v>14.49200884676797</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.03455875870580975</v>
+      </c>
+      <c r="W97">
+        <v>0.2305473684210526</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2303917247053983</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2763979721031463</v>
+      </c>
+      <c r="C98">
+        <v>-17.61482069671868</v>
+      </c>
+      <c r="D98">
+        <v>5.885179303281316</v>
+      </c>
+      <c r="E98">
+        <v>22.7</v>
+      </c>
+      <c r="F98">
+        <v>36</v>
+      </c>
+      <c r="G98">
+        <v>12.5</v>
+      </c>
+      <c r="H98">
+        <v>24.2</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1.94</v>
+      </c>
+      <c r="K98">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L98">
+        <v>1.96</v>
+      </c>
+      <c r="M98">
+        <v>8.5968</v>
+      </c>
+      <c r="N98">
+        <v>-6.6368</v>
+      </c>
+      <c r="O98">
+        <v>-0.9955200000000002</v>
+      </c>
+      <c r="P98">
+        <v>-5.64128</v>
+      </c>
+      <c r="Q98">
+        <v>-5.66128</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.374749302578654</v>
+      </c>
+      <c r="T98">
+        <v>18.11501105845992</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.03419877163595757</v>
+      </c>
+      <c r="W98">
+        <v>0.2306333333333334</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2279918109063838</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2783979721031462</v>
+      </c>
+      <c r="C99">
+        <v>-18.03894614842115</v>
+      </c>
+      <c r="D99">
+        <v>5.836053851578848</v>
+      </c>
+      <c r="E99">
+        <v>23.075</v>
+      </c>
+      <c r="F99">
+        <v>36.375</v>
+      </c>
+      <c r="G99">
+        <v>12.5</v>
+      </c>
+      <c r="H99">
+        <v>24.2</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1.94</v>
+      </c>
+      <c r="K99">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L99">
+        <v>1.96</v>
+      </c>
+      <c r="M99">
+        <v>8.686350000000001</v>
+      </c>
+      <c r="N99">
+        <v>-6.726350000000001</v>
+      </c>
+      <c r="O99">
+        <v>-1.0089525</v>
+      </c>
+      <c r="P99">
+        <v>-5.717397500000001</v>
+      </c>
+      <c r="Q99">
+        <v>-5.7373975</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.820065736771539</v>
+      </c>
+      <c r="T99">
+        <v>24.15334807794656</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.03384620697991677</v>
+      </c>
+      <c r="W99">
+        <v>0.2307175257731959</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2256413798661118</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2803979721031462</v>
+      </c>
+      <c r="C100">
+        <v>-18.46225825800365</v>
+      </c>
+      <c r="D100">
+        <v>5.787741741996347</v>
+      </c>
+      <c r="E100">
+        <v>23.45</v>
+      </c>
+      <c r="F100">
+        <v>36.75</v>
+      </c>
+      <c r="G100">
+        <v>12.5</v>
+      </c>
+      <c r="H100">
+        <v>24.2</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1.94</v>
+      </c>
+      <c r="K100">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L100">
+        <v>1.96</v>
+      </c>
+      <c r="M100">
+        <v>8.7759</v>
+      </c>
+      <c r="N100">
+        <v>-6.8159</v>
+      </c>
+      <c r="O100">
+        <v>-1.022385</v>
+      </c>
+      <c r="P100">
+        <v>-5.793515</v>
+      </c>
+      <c r="Q100">
+        <v>-5.813515000000001</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.710698605157309</v>
+      </c>
+      <c r="T100">
+        <v>36.23002211691984</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.03350083752093803</v>
+      </c>
+      <c r="W100">
+        <v>0.2308</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.2233389168062535</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2823979721031463</v>
+      </c>
+      <c r="C101">
+        <v>-18.8847770586901</v>
+      </c>
+      <c r="D101">
+        <v>5.740222941309894</v>
+      </c>
+      <c r="E101">
+        <v>23.825</v>
+      </c>
+      <c r="F101">
+        <v>37.125</v>
+      </c>
+      <c r="G101">
+        <v>12.5</v>
+      </c>
+      <c r="H101">
+        <v>24.2</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1.94</v>
+      </c>
+      <c r="K101">
+        <v>-0.02000000000000002</v>
+      </c>
+      <c r="L101">
+        <v>1.96</v>
+      </c>
+      <c r="M101">
+        <v>8.865450000000001</v>
+      </c>
+      <c r="N101">
+        <v>-6.905450000000001</v>
+      </c>
+      <c r="O101">
+        <v>-1.0358175</v>
+      </c>
+      <c r="P101">
+        <v>-5.869632500000001</v>
+      </c>
+      <c r="Q101">
+        <v>-5.889632500000001</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.382597210314618</v>
+      </c>
+      <c r="T101">
+        <v>72.46004423383968</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.03316244522274674</v>
+      </c>
+      <c r="W101">
+        <v>0.2308808080808081</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2210829681516449</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
